--- a/vendor-verdict-audit.xlsx
+++ b/vendor-verdict-audit.xlsx
@@ -1,41 +1,788 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jcnmacbook/watchtower-peptides/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFB4EAF1-1E97-094A-BEC4-4BB2F51DC9B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-35520" yWindow="-20280" windowWidth="29340" windowHeight="19100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="Vendor Verdict Audit" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="252">
+  <si>
+    <t>Vendor</t>
+  </si>
+  <si>
+    <t>Score</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>COA Tier</t>
+  </si>
+  <si>
+    <t>LV</t>
+  </si>
+  <si>
+    <t>PQ</t>
+  </si>
+  <si>
+    <t>TR</t>
+  </si>
+  <si>
+    <t>CX</t>
+  </si>
+  <si>
+    <t>Verdict</t>
+  </si>
+  <si>
+    <t>Audit Notes</t>
+  </si>
+  <si>
+    <t>Audited At</t>
+  </si>
+  <si>
+    <t>Bulk Peptide Supply</t>
+  </si>
+  <si>
+    <t>active</t>
+  </si>
+  <si>
+    <t>Bulk Peptide Supply publicly discloses ownership, lists a physical address, and covers seven products through Finnrick-verified third-party testing — a cleaner transparency profile than most vendors at this score level. Average purity is 99.4% across seven tests. The gaps are minor: no published contact information, and test coverage is still relatively thin for a catalog of this size. A reliable baseline with room to grow.</t>
+  </si>
+  <si>
+    <t>T4 — Finnrick chain-of-custody, no audit required</t>
+  </si>
+  <si>
+    <t>Polaris Peptides</t>
+  </si>
+  <si>
+    <t>Polaris runs COAs per product rather than linking to a single page — each listing has its own Chromate Analytics or Janoshik report, and nine products have Finnrick endotoxin test results on top of that. Purity data we've reviewed averages 99.4% across eleven tested peptides with no failures. Access to the COA page itself requires a free account login, which is an extra step but not unusual for a members-model vendor. Ownership is publicly disclosed. This is one of the most comprehensively documented vendors in our database.</t>
+  </si>
+  <si>
+    <t>EZ Peptides</t>
+  </si>
+  <si>
+    <t>EZ Peptides publishes third-party lab results backed by Finnrick verification across six tested products, and the company lists a physical US address. Most purity results are solid, but one retatrutide batch came back at 93.2% — below the 95% threshold where we start flagging product quality. Whether that's a one-time outlier or a sign of inconsistency requires more data points. No named ownership. The testing infrastructure is real; we'd want to see that retatrutide result addressed before ranking this higher.</t>
+  </si>
+  <si>
+    <t>Orbitrex Peptides</t>
+  </si>
+  <si>
+    <t>Orbitrex operates from Iceland, which means purchases fall outside US consumer protection frameworks — worth knowing before you order. On the chemistry side, the record is nearly spotless: 99.89% average purity across seven Finnrick-verified tests, with batch-specific COAs and methodology documentation. A physical address is on file but there's no published contact information. The jurisdiction risk is real; the testing evidence isn't.</t>
+  </si>
+  <si>
+    <t>NextechLabs</t>
+  </si>
+  <si>
+    <t>NextechLabs has strong testing numbers — 99.69% average across seven Finnrick-verified products — but no publicly accessible COA archive. We couldn't locate an active COA page, which means the documentation exists in Finnrick's system but isn't independently browsable. No contact information, no ownership disclosure. The purity record is clean; the transparency infrastructure around it is thin. We'd want a working COA page before ranking this higher.</t>
+  </si>
+  <si>
+    <t>Aavant Research</t>
+  </si>
+  <si>
+    <t>Aavant Research posts some of the cleanest purity numbers in our dataset — 99.87% average across seven Finnrick-verified tests, including multiple tirzepatide and retatrutide runs. Contact information is public; no physical address or ownership disclosure. The testing record alone would rank them higher if the company identity were clearer. As it stands, you're buying from a well-tested vendor whose principals are unknown.</t>
+  </si>
+  <si>
+    <t>Omegamino</t>
+  </si>
+  <si>
+    <t>Omegamino meets the basic requirements: third-party testing, batch numbers, methodology disclosed. Purity averages 99.8% across the four products we have data for, which is solid. But four Finnrick-verified tests is the minimum we'd accept, and there's no contact information, no physical address, and no ownership disclosure. The testing data is good; the company identity is a blank. Sufficient for cautious buyers, not a vendor we'd recommend over better-documented alternatives.</t>
+  </si>
+  <si>
+    <t>Astro Peptides</t>
+  </si>
+  <si>
+    <t>Two CJC-1295 batches came back at 88.99% and 85.65% purity — the lowest results in our dataset for any vendor in this group. Both failures were from the same testing date, which suggests a bad batch rather than a systematic problem, but neither has been publicly acknowledged. Other tested products look clean. No COA page is publicly accessible, no contact information, and no address or ownership on file. The CJC-1295 results need an explanation before this vendor earns a stronger recommendation.</t>
+  </si>
+  <si>
+    <t>RUO Science</t>
+  </si>
+  <si>
+    <t>T3</t>
+  </si>
+  <si>
+    <t>RUO Science uses Freedom Diagnostics as their third-party testing laboratory — a US-based lab with a public searchable COA archive. Batch-specific documents are accessible and show real purity data: BPC-157 at 99.12% and Tirzepatide at 99.74% in reviewed samples. Testing methodology includes HPLC, mass spectrometry, endotoxin, sterility, and heavy metals. No business address or ownership disclosure on the site, which limits accountability. The lab is now confirmed; the transparency gaps around the business itself remain. A solid testing record that was previously undersold by an earlier incomplete assessment.</t>
+  </si>
+  <si>
+    <t>Freedom Diagnostics confirmed via downloaded webp. Lot LCARN500-02122026-J, searchable at FreedomDiagnosticsTesting.com. HPLC-UV-MS, mass spec included, chromatogram present. Multiple labs used across product line (MB/VP batch prefixes suggest MZ Biolabs and Vanguard also).</t>
+  </si>
+  <si>
+    <t>2026-06-11</t>
+  </si>
+  <si>
+    <t>Simple Peptide</t>
+  </si>
+  <si>
+    <t>Simple Peptide has seven Finnrick-verified tests, an active COA page, contact info, a physical address, and lab methodology disclosed — a cleaner checklist than most vendors near this score. The gap is purity data: we haven't extracted raw numbers from their COA archive yet, so the score reflects Finnrick's independent testing footprint rather than confirmed purity percentages. No ownership disclosure.</t>
+  </si>
+  <si>
+    <t>Glacier Aminos</t>
+  </si>
+  <si>
+    <t>T1</t>
+  </si>
+  <si>
+    <t>Third-party testing through Kovera Labs and Freedom Diagnostics — two named labs, which is more lab diversification than most vendors at this score level. Three tests averaging 99.7% purity. Contact info is public; no physical address or ownership. The sample is thin for a full catalog recommendation but the existing results are clean.</t>
+  </si>
+  <si>
+    <t>batch numbers present; no known lab name found in page text or PDFs — may be vendor-branded</t>
+  </si>
+  <si>
+    <t>Mile High Compounds</t>
+  </si>
+  <si>
+    <t>Chromate Analytics COAs, five tests averaging 99.4% purity. Ownership is disclosed and a physical address is on file. Iceland-based operation (.is domain) — no US consumer protection recourse. No contact information published. The testing data is solid; the jurisdiction and missing contact info are the flags.</t>
+  </si>
+  <si>
+    <t>no known lab name found in page text or PDFs — may be vendor-branded</t>
+  </si>
+  <si>
+    <t>Ion Peptide</t>
+  </si>
+  <si>
+    <t>Three different named third-party labs — ILS Laboratories, Kovera Labs, and Freedom Diagnostics — across six tests averaging 99.7% purity. A physical address is on file. No contact info or ownership disclosure. The lab diversification is a genuine differentiator; most vendors this size pick one lab and stick with it.</t>
+  </si>
+  <si>
+    <t>Paramount Peptides</t>
+  </si>
+  <si>
+    <t>Paramount has more Finnrick endotoxin tests than most vendors above it in the rankings — eight total — and both a physical address and contact information are listed. The problem is purity data: we have none in our database. Whether that's a gap in our scraping or a sign that HPLC results aren't publicly available, we can't independently confirm product purity. No ownership disclosure. The infrastructure is there; the chemistry documentation needs to catch up.</t>
+  </si>
+  <si>
+    <t>Loti Labs</t>
+  </si>
+  <si>
+    <t>Loti Labs is one of the more transparent operators in this space — ownership disclosed, contact info public, address on file, Finnrick-verified. That makes the CJC-1295 results harder to explain: two separate batches came back below 62% purity. At those levels the product is mostly something else. Their other tested peptides look clean. Until Loti addresses those CJC-1295 results publicly, we can't recommend them for that peptide specifically.</t>
+  </si>
+  <si>
+    <t>Peptidology</t>
+  </si>
+  <si>
+    <t>Peptidology operates out of Scottsdale, AZ and runs third-party testing through an ISO-17025 accredited lab. Their COA library has 426 documents on file, all batch-specific. Purity average across seven tested products is 99.5% with no failures. Seven Finnrick-verified tests add an independent layer of confirmation. Ownership isn't disclosed, which is the only transparency gap in an otherwise strong profile. One of the better-documented vendors in this space.</t>
+  </si>
+  <si>
+    <t>Paradigm Peptides</t>
+  </si>
+  <si>
+    <t>flagged</t>
+  </si>
+  <si>
+    <t>Verified Peptides</t>
+  </si>
+  <si>
+    <t>Eight Finnrick-verified tests and an active COA page, but the operator is almost entirely anonymous — no contact info, no address, no ownership disclosure. The Finnrick coverage is meaningful for confirming a lab testing relationship exists, but without purity data in our database we can't confirm the actual numbers. Worth watching as more data surfaces.</t>
+  </si>
+  <si>
+    <t>Peptide Crafters</t>
+  </si>
+  <si>
+    <t>Seven Finnrick-verified tests and an active COA page. Contact info is public. No physical address or ownership disclosure. We don't have purity data in our database from their COA archive, so the score is driven by Finnrick footprint rather than confirmed percentages. The infrastructure is there; the documentation needs to be more publicly accessible.</t>
+  </si>
+  <si>
+    <t>Ascension Peptides</t>
+  </si>
+  <si>
+    <t>Testing is conducted by Kovera Labs — a named third-party laboratory producing full-panel COAs with RP-HPLC chromatograms, LC-MS identity confirmation, endotoxin screening (≤0.5 EU/mL), microbial sterility, and heavy metal testing (As, Cd, Pb, Hg). Batch numbers are specific and dated. Purity results average above 99.5% across 50+ reviewed documents. The COA page sits behind an age gate, which limits casual browsing, but the documentation quality inside is among the higher-tier vendors reviewed. No physical address or ownership disclosure — that is the remaining transparency gap. Score will rise further if Kovera Labs accreditation is confirmed in the A2LA or PJLA registry.</t>
+  </si>
+  <si>
+    <t>Kovera Labs (KVR-2026-XXXXXX report numbers). Full COA panel: RP-HPLC purity, Net Content, LC-MS identity, endotoxin (≤0.5 EU/mL, PASS), microbial sterility, heavy metals (As/Cd/Pb/Hg). Real chromatograms visible. Batch-specific lot numbers. Accreditation (A2LA/PJLA) not yet verified — upgrade to T3 if Kovera Labs confirmed ISO 17025.</t>
+  </si>
+  <si>
+    <t>Felix Chemical Supply</t>
+  </si>
+  <si>
+    <t>Felix uses two independently verified labs — Freedom Diagnostics and Chromate Analytical — and labels each batch entry explicitly by which lab ran the test. A subset of batches are dual-tested by both labs on the same lot, which is a notably high verification standard. Per-product COA pages contain a full historical archive with batch-specific identifiers. Florida-based (Saint Augustine, FL). Pricing runs at the low end of the market. The primary gap is ownership disclosure, which is not public. Strong lab transparency for the price point.</t>
+  </si>
+  <si>
+    <t>Freedom Diagnostics (Freedom Labs) + Chromate Analytical (Chromate Labs) — both confirmed T3 labs. Per-batch COA pages with explicit lab labeling on each entry. Batch 081925-BPC-6 dual-tested by both labs simultaneously. Extensive historical archive across all products. Strong T3, approaching T4.</t>
+  </si>
+  <si>
+    <t>Peptide Partners</t>
+  </si>
+  <si>
+    <t>Ownership is disclosed, contact info is public, and Finnrick-verified testing backs the lab transparency claim. No publicly accessible COA page at the time of review, which is a gap — COA documentation should be independently browsable. No physical address on file. Sufficient identity transparency for the score, but the missing COA archive limits how much we can confirm independently.</t>
+  </si>
+  <si>
+    <t>Nuscience Peptides</t>
+  </si>
+  <si>
+    <t>Ten Finnrick-verified tests. No company identity disclosed — no contact info, no address, no ownership. COA page exists but we have no purity data extracted from it. Free shipping on all orders. The Finnrick coverage is real, but the operator is completely anonymous. Worth watching, not ready to recommend.</t>
+  </si>
+  <si>
+    <t>Prime Peptides</t>
+  </si>
+  <si>
+    <t>Skye Peptides</t>
+  </si>
+  <si>
+    <t>Seventy-five Finnrick-verified tests across 10 compounds — one of the highest testing footprints we track. Results are mixed: GLP-1 peptides (Semaglutide, Tirzepatide, Retatrutide) score A Great, but BPC-157 — their most popular product — rates E Bad with a minimum score of 2.6/10 across 12 tests. Ipamorelin and CJC-1295 rate B and C respectively. Zero company identity: no contact info, no address, no ownership disclosure, no lab named on-site. High testing footprint, notable quality concerns on core healing peptides, no company identity whatsoever.</t>
+  </si>
+  <si>
+    <t>Biotech Peptides</t>
+  </si>
+  <si>
+    <t>Contact info, a physical address, and lab disclosure are all confirmed — one of the more complete identity profiles at this score level. COA page is active. No Finnrick testing, and we have no purity data in our database. Good baseline legitimacy, but without confirmed purity numbers the chemistry side is unverified.</t>
+  </si>
+  <si>
+    <t>Crush Research</t>
+  </si>
+  <si>
+    <t>Ownership and contact info are both public, and the COA page is active. No Finnrick testing and no purity data in our database. The company identity is solid for this tier; the chemistry documentation isn't comprehensive enough to verify product quality independently.</t>
+  </si>
+  <si>
+    <t>Swiss Chems</t>
+  </si>
+  <si>
+    <t>Two CJC-1295 batches tested below 58% purity — not borderline results, these are failures. A product at 57% purity is mostly not what it's labeled. Other tested peptides look cleaner. Contact info is public, but no physical address or ownership. Do not buy CJC-1295 from Swiss Chems; the rest of the catalog requires more data before recommending.</t>
+  </si>
+  <si>
+    <t>Sports Technology Labs</t>
+  </si>
+  <si>
+    <t>Physical address and ownership both disclosed — more accountability than most vendors near this score. COA page is active. No Finnrick testing, no purity data in our database. Pricing runs at the high end of the market. The identity checks out; the testing record needs work to justify the price premium.</t>
+  </si>
+  <si>
+    <t>MZ Biolabs COA confirmed via downloaded webp. Lot number 2025-10-06, HPLC-UV-MS, analyst Ken Pendarvis ChE. Real chromatogram with baseline noise. QR proof-of-authenticity.</t>
+  </si>
+  <si>
+    <t>Nexaph</t>
+  </si>
+  <si>
+    <t>COAs are hosted on SwiftCS (nexaph.coa.swiftcs.ai), a third-party COA verification platform — an unusual approach but a real one. Ten Finnrick-verified tests. No address, no ownership, and no lab named on the vendor's own site. Above-market pricing. The Finnrick coverage is the strongest signal here; everything else about the company identity is absent.</t>
+  </si>
+  <si>
+    <t>Pure Rawz</t>
+  </si>
+  <si>
+    <t>Seven Finnrick-verified tests suggest a real lab testing relationship exists. The COA page was inaccessible at review time — Cloudflare blocking — so we can't confirm what's there. No contact info, no address, no ownership. One of the larger catalogs in this space; the anonymity is a significant concern given the scale of the operation.</t>
+  </si>
+  <si>
+    <t>True Research Labs</t>
+  </si>
+  <si>
+    <t>COAs are tested by Horizon Analytical — a US-based lab issuing UPLC/MS reports with batch-specific identifiers. Testing methodology is disclosed and results are accessible through per-product document links. Business address confirmed (Sheridan, WY). However, the COA page requires JavaScript navigation and results are not browsable without clicking through individual product buttons. Ownership disclosure is absent. Score of 46 reflects a confirmed T3 lab with incomplete operational transparency. The right foundations are in place; documentation accessibility needs work before this vendor warrants a stronger recommendation.</t>
+  </si>
+  <si>
+    <t>Horizon Analytical confirmed via PDF download. Lot TRL-9907743, Aleksey Yevtodiyenko PhD. UPLC/MS, full chromatogram + mass spec on page 2. Searchable at horizonanalytical.com. Analysis date 05/12/2026.</t>
+  </si>
+  <si>
+    <t>Certified Pep</t>
+  </si>
+  <si>
+    <t>Certified Pep uses Vanguard Laboratory — ISO/IEC 17025:2017 accredited, with named testing for purity, endotoxins, heavy metals, and bacteria. That's one of the most specific lab disclosures in this tier. Site is Cloudflare-protected so products and pricing couldn't be directly verified; score reflects the transparency record rather than a full catalog review. If pricing and product breadth are competitive, this vendor would score in the 45–60 range once we can access the full data. The lab disclosure alone puts them above most vendors at a similar overall score.</t>
+  </si>
+  <si>
+    <t>Lab: Vanguard; batch numbers present</t>
+  </si>
+  <si>
+    <t>Amino Asylum</t>
+  </si>
+  <si>
+    <t>Perfect Peptides</t>
+  </si>
+  <si>
+    <t>COAs are tested by Chromate Analytical, confirmed via direct document inspection. Lab name and batch information are present in reviewed documents. The score of 38 reflects near-zero purity data in our database and incomplete transparency flags — no ownership disclosure, no business address, and no community testing record. The lab is legitimate; the surrounding documentation infrastructure is not built out. A T3 lab operating with a T1 disclosure profile. Worth monitoring as data accumulates, not a vendor we can recommend yet.</t>
+  </si>
+  <si>
+    <t>Chromate Analytical confirmed via downloaded PNG. Certificate #34141, access PERFECT88HGR at chromate.org/verify. Batch PP6896266. Full panel: purity 99.294%, endotoxins 7.65 EU/vial, metals &lt;5ppb. Chromatogram present.</t>
+  </si>
+  <si>
+    <t>Licensed Peptides</t>
+  </si>
+  <si>
+    <t>T2</t>
+  </si>
+  <si>
+    <t>Licensed Peptides has a confirmed physical address (Boca Raton, FL), a phone number, and describes a 6-point verification process (HPLC, mass spec, endotoxin, sterility checks). Lot numbers appear on purity reports. The problem: no third-party testing lab is ever named — the purity reports are branded as 'Licensed Peptides Reports,' which means we can't confirm the testing was done by an independent party. The product catalog is also sold exclusively in 10-vial packs, which inflates apparent pricing relative to per-vial vendors. Good operational transparency, weak lab independence. Score will rise significantly if they publish the lab name.</t>
+  </si>
+  <si>
+    <t>Vanguard Laboratory COAs confirmed visually — legitimate lab, ISO 17025, A2LA #6377.01. BUT lot numbers are cap colors (Red Cap, Green Cap) not batch IDs — fails batch traceability. T2 until proper lot numbers confirmed. Chromatogram obscured by Licensed Peptides watermark.</t>
+  </si>
+  <si>
+    <t>Core Peptides</t>
+  </si>
+  <si>
+    <t>Third-party lab testing with contact info and a physical address on file. COA page is active. No Finnrick testing. The lab verification is real but not batch-specific — meaning the same COA applies to multiple production runs, which limits how precisely you can trace what you're getting. A legitimate vendor with documentation that needs to go one level deeper.</t>
+  </si>
+  <si>
+    <t>Cernum Biosciences</t>
+  </si>
+  <si>
+    <t>Cernum Biosciences lists certificates of analysis on their website, but those COAs are issued by their own internal "Lab Research Department" — not an independent third-party lab. Every product on the site carries the identical batch number (201-139-35496), which means their batch tracking is a template, not a real audit trail. A 2026 press release placed on USA Today's paid wire service claims "independent third-party verification" and "batch-level traceability" — both directly contradicted by the actual COA documents. Cernum is a newer vendor with no community track record. Until genuine third-party lab results appear, we recommend looking elsewhere.</t>
+  </si>
+  <si>
+    <t>LVLUP Health</t>
+  </si>
+  <si>
+    <t>No COA page and no lab testing documentation of any kind. Ownership is disclosed. There's not enough evidence to evaluate product quality — we can verify who runs it but not what they're selling. Not recommended until testing documentation appears.</t>
+  </si>
+  <si>
+    <t>T0 — no COA exists, nothing to verify</t>
+  </si>
+  <si>
+    <t>Limitless Biotech</t>
+  </si>
+  <si>
+    <t>No COA page, no lab testing documentation. Contact info is public. Payments are PayPal-only, which limits transaction protection compared to credit card purchases. Not enough evidence to evaluate product quality. Not recommended without third-party testing.</t>
+  </si>
+  <si>
+    <t>Healthgevity</t>
+  </si>
+  <si>
+    <t>No COA page, no lab testing, no physical address. Claims to offer research-grade peptides but provides no independent verification. Not recommended.</t>
+  </si>
+  <si>
+    <t>Penguin Peptides</t>
+  </si>
+  <si>
+    <t>COA page exists, and a physical address is on file. No third-party lab verification — internal testing only. No Finnrick testing. Without independent confirmation, the COA documents cannot be treated as reliable quality evidence.</t>
+  </si>
+  <si>
+    <t>Alpha BioMed Labs</t>
+  </si>
+  <si>
+    <t>Institutional-access-only catalog — products are not publicly purchasable at this time. Listed for completeness. No public documentation available to evaluate.</t>
+  </si>
+  <si>
+    <t>Dynamic Peptide</t>
+  </si>
+  <si>
+    <t>No COA, no lab testing of any kind, no contact info, no address, no ownership disclosure. One of the least-documented vendors in our database. We have no basis for evaluating product quality. Avoid.</t>
+  </si>
+  <si>
+    <t>Southern Peptides</t>
+  </si>
+  <si>
+    <t>No documentation of any kind: no COA, no lab testing, no contact info, no address, no ownership. Lowest-scored vendor in our database. Avoid.</t>
+  </si>
+  <si>
+    <t>Maxx Research Supply</t>
+  </si>
+  <si>
+    <t>Maxx Research Supply (maxxresearchsupply.com) could not be accessed due to Cloudflare protection, is not indexed in public search, and has no presence in third-party review databases. No products, no prices, and no documentation of any kind are verifiable. Score of 5 reflects no data, not confirmed problems. We recommend waiting for more information before using this vendor.</t>
+  </si>
+  <si>
+    <t>Apollo Peptide Sciences</t>
+  </si>
+  <si>
+    <t>Pivot Labs</t>
+  </si>
+  <si>
+    <t>Assessment</t>
+  </si>
+  <si>
+    <t>Issues Identified</t>
+  </si>
+  <si>
+    <t>Recommended Revision</t>
+  </si>
+  <si>
+    <t>Clear and factual. Measured tone. 'A reliable baseline with room to grow' is the weakest close in the dataset — it reads like a school report card.</t>
+  </si>
+  <si>
+    <t>'Reliable baseline with room to grow' is vague and soft. Visitors don't know what 'baseline' means in context. The verdict earns credibility in the first three sentences then loses it.</t>
+  </si>
+  <si>
+    <t>Bulk Peptide Supply publicly discloses ownership, lists a physical address, and covers seven products through Finnrick-verified third-party testing. Average purity across those seven tests is 99.4%. The gaps are minor: no published contact information, and test coverage is thin relative to catalog size. Strong record for the score level; transparency infrastructure has room to expand.</t>
+  </si>
+  <si>
+    <t>Well-structured and specific. 'Most comprehensively documented vendors in our database' is the strongest close in the top tier. Minor: 'members-model vendor' is jargon a first-time visitor won't parse.</t>
+  </si>
+  <si>
+    <t>'On top of that' is colloquial. 'Members-model vendor' needs plain-language translation.</t>
+  </si>
+  <si>
+    <t>Polaris runs COAs per product rather than through a centralized archive — each listing carries its own Chromate Analytics or Janoshik report, with Finnrick endotoxin results across nine products adding an independent confirmation layer. Purity data across eleven tested peptides averages 99.4% with no failures. Accessing the COA page requires a free account, which is an extra step but not unusual for this vendor type. Ownership is publicly disclosed. Among the most comprehensively documented vendors in our database.</t>
+  </si>
+  <si>
+    <t>Factual and appropriately hedged. 'The testing infrastructure is real' sounds defensive. 'Requires more data points' reads like internal analyst notes.</t>
+  </si>
+  <si>
+    <t>'The testing infrastructure is real' pre-empts doubt in a way that introduces it. 'We'd want to see that retatrutide result addressed before ranking this higher' is editorial and informal.</t>
+  </si>
+  <si>
+    <t>EZ Peptides publishes third-party lab results with Finnrick verification across six tested products. The company lists a physical US address. Most purity results are solid, but one retatrutide batch returned 93.2% — below the 95% benchmark we use for top-tier vendors. Whether that reflects a one-time production issue or a broader inconsistency requires additional data. No ownership disclosure on file. The testing record is substantive; that retatrutide result warrants monitoring.</t>
+  </si>
+  <si>
+    <t>Strong. Iceland jurisdiction risk communicated plainly. The close — 'The jurisdiction risk is real; the testing evidence isn't' — is one of the best lines in the dataset.</t>
+  </si>
+  <si>
+    <t>Minor: 'worth knowing before you order' is slightly paternalistic. 'On the chemistry side' is casual.</t>
+  </si>
+  <si>
+    <t>Orbitrex operates from Iceland, placing purchases outside US consumer protection frameworks — a material consideration before ordering. On testing, the record is nearly spotless: 99.89% average purity across seven Finnrick-verified tests, with batch-specific COAs and methodology documentation. A physical address is on file; no published contact information. The jurisdiction risk is real. The testing evidence is not.</t>
+  </si>
+  <si>
+    <t>Clear and accurate. 'Exists in Finnrick's system but isn't independently browsable' is exactly the right nuance — demonstrates methodology rigor. Minor: 'We couldn't locate' is informal and inserts process narration.</t>
+  </si>
+  <si>
+    <t>'We couldn't locate an active COA page' reads as a procedural note rather than a finding. Rephrase as a factual state.</t>
+  </si>
+  <si>
+    <t>NextechLabs has strong testing numbers — 99.69% average across seven Finnrick-verified products — but no publicly accessible COA archive. Documentation exists in Finnrick's system but is not independently browsable by researchers. No contact information or ownership disclosure on file. The purity record is clean; the transparency infrastructure around it is not. A working COA page would materially improve this score.</t>
+  </si>
+  <si>
+    <t>Well-written. 'You're buying from a well-tested vendor whose principals are unknown' is the most memorable close in the mid-tier — direct and specific.</t>
+  </si>
+  <si>
+    <t>Minor tension: 'some of the cleanest purity numbers in our dataset' opens with high praise that the identity gap partially walks back. The juxtaposition is intentional but could be sharpened.</t>
+  </si>
+  <si>
+    <t>Aavant Research posts some of the strongest purity numbers in our database — 99.87% average across seven Finnrick-verified tests, including multiple tirzepatide and retatrutide runs. Contact information is public; no physical address or ownership disclosure on file. The testing record alone would place this vendor higher if the operator identity were clearer. The chemistry is well-documented. The company behind it is not.</t>
+  </si>
+  <si>
+    <t>Accurate and well-structured. 'The company identity is a blank' is a good close. 'Sufficient for cautious buyers' is appropriately hedged.</t>
+  </si>
+  <si>
+    <t>'Meets the basic requirements' is dismissive as an opener. 'Not a vendor we'd recommend over better-documented alternatives' buries the cautionary message.</t>
+  </si>
+  <si>
+    <t>Omegamino meets the minimum documentation threshold: third-party testing, batch numbers, methodology disclosed. Purity averages 99.8% across four Finnrick-verified products — a solid result on a thin sample. No contact information, physical address, or ownership disclosure. Four tests is the floor for Tier 4 consideration, not a ceiling. The testing data is good. The company identity is largely undocumented. Sufficient for cautious buyers; not a vendor we'd rank above better-documented alternatives.</t>
+  </si>
+  <si>
+    <t>Strong. 'Bad batch rather than a systematic problem' framing shows analytical restraint. The close is well-calibrated.</t>
+  </si>
+  <si>
+    <t>'The lowest results in our dataset for any vendor in this group' is a comparative superlative that will become inaccurate as the database grows.</t>
+  </si>
+  <si>
+    <t>Two CJC-1295 batches returned 88.99% and 85.65% purity — both from the same testing date, suggesting a production batch issue rather than a systemic pattern. Neither result has been publicly acknowledged by the vendor. Other tested products look clean. No publicly accessible COA page, no contact information, and no address or ownership on file. The CJC-1295 results require a public response before this vendor earns a stronger score.</t>
+  </si>
+  <si>
+    <t>Detailed and specific. 'Previously undersold by an earlier incomplete assessment' is transparent and trust-building. The five-method list reads as a spec sheet — most visitors will skim it.</t>
+  </si>
+  <si>
+    <t>Listing HPLC, mass spec, endotoxin, sterility, and heavy metals consecutively buries the key finding inside methodology detail. Condense to signal comprehensiveness without enumerating.</t>
+  </si>
+  <si>
+    <t>RUO Science tests through Freedom Diagnostics — a US-based lab with a searchable public COA archive. Batch-specific documents show real purity data: BPC-157 at 99.12% and Tirzepatide at 99.74% in reviewed samples. Full-panel methodology is confirmed. No business address or ownership disclosure on the site. A solid and previously underrated testing record; transparency gaps around the business identity remain.</t>
+  </si>
+  <si>
+    <t>Honest about the data gap. 'Score reflects Finnrick's independent testing footprint rather than confirmed purity percentages' is a model of methodological transparency.</t>
+  </si>
+  <si>
+    <t>Structure is slightly inverted — positives listed first, critical data gap buried in the middle. A skimming visitor may miss the limitation.</t>
+  </si>
+  <si>
+    <t>Simple Peptide has seven Finnrick-verified tests, an active COA page, contact info, a physical address, and disclosed lab methodology — a strong transparency checklist for this tier. The current score is limited by one gap: raw purity percentages have not yet been extracted from their COA archive. Until confirmed, the score reflects testing footprint rather than verified purity. No ownership disclosure on file. Transparency infrastructure is above average; score will likely rise as purity data is captured.</t>
+  </si>
+  <si>
+    <t>Appropriately brief given thin data. 'More lab diversification than most vendors at this score level' is a useful differentiator.</t>
+  </si>
+  <si>
+    <t>'The sample is thin for a full catalog recommendation but the existing results are clean' reads as an apology for the score rather than a clear verdict.</t>
+  </si>
+  <si>
+    <t>Glacier Aminos uses two named third-party labs — Kovera and Freedom Diagnostics — which is more lab diversification than most vendors at this score level. Three tests averaging 99.7% purity. Contact info is public; no physical address or ownership on file. Results are clean; sample size is too small to support a broad recommendation. Score will move as additional tests accumulate.</t>
+  </si>
+  <si>
+    <t>Solid. Iceland jurisdiction flag handled appropriately. Structure mirrors Orbitrex correctly given the similarity.</t>
+  </si>
+  <si>
+    <t>'No contact information published' is slightly buried as the final item in a trailing list — it is a meaningful flag.</t>
+  </si>
+  <si>
+    <t>Mile High Compounds uses Chromate Analytics for third-party testing — five tests averaging 99.4% purity, with ownership disclosed and a physical address on file. Iceland-based operation (.is domain), meaning purchases fall outside US consumer protection frameworks. No contact information published. The testing data is solid; the jurisdiction and missing contact info are meaningful flags.</t>
+  </si>
+  <si>
+    <t>The three-lab observation is a genuine differentiator and is correctly highlighted. Clean and factual.</t>
+  </si>
+  <si>
+    <t>'Most vendors this size pick one lab and stick with it' is an unsupported comparative claim without cited basis.</t>
+  </si>
+  <si>
+    <t>Ion Peptide uses three independently named third-party labs — ILS Laboratories, Kovera Labs, and Freedom Diagnostics — across six tests averaging 99.7% purity. A physical address is on file. No contact information or ownership disclosure. The lab diversification is a genuine differentiator in this tier.</t>
+  </si>
+  <si>
+    <t>The 'gaps in our scraping vs. publicly unavailable' distinction is intellectually honest and appropriate for a methodology-forward brand.</t>
+  </si>
+  <si>
+    <t>'Whether that's a gap in our scraping or a sign that HPLC results aren't publicly available' introduces doubt about the platform's own data reliability. Tighten this.</t>
+  </si>
+  <si>
+    <t>Paramount has eight Finnrick endotoxin tests — above average for this tier — with both a physical address and contact information on file. The current limitation is purity data: confirmed HPLC results are not in our database. Until purity percentages can be independently verified, the score reflects testing footprint and transparency rather than confirmed product quality. No ownership disclosure on file.</t>
+  </si>
+  <si>
+    <t>The CJC-1295 results are reported with appropriate alarm. 'The product is mostly something else' is one of the most impactful lines in the dataset — keep it.</t>
+  </si>
+  <si>
+    <t>Minor: 'makes the CJC-1295 results harder to explain' is slightly casual.</t>
+  </si>
+  <si>
+    <t>Loti Labs is among the more transparent operators in this tier — ownership disclosed, contact info public, address on file, Finnrick-verified. That makes the CJC-1295 results significant: two separate batches returned below 62% purity. At those concentrations, the product is largely mislabeled. Other tested peptides look clean. Until Loti publicly addresses the CJC-1295 data, we do not recommend that product from this vendor.</t>
+  </si>
+  <si>
+    <t>Strong. ISO-17025 note and 426-document library are specific and credibility-building. Well-calibrated close.</t>
+  </si>
+  <si>
+    <t>Minor: 'One of the better-documented vendors in this space' as a close is a superlative that will age poorly as the database expands.</t>
+  </si>
+  <si>
+    <t>Peptidology operates from Scottsdale, AZ and tests through an ISO/IEC 17025 accredited laboratory. Their COA library contains 426 batch-specific documents. Purity across seven independently tested products averages 99.5% with no failures, and Finnrick verification adds a second independent confirmation layer. The only transparency gap is ownership disclosure. Among the strongest documentation profiles in this tier.</t>
+  </si>
+  <si>
+    <t>Accurate. The testing footprint vs. purity data tension is explained appropriately.</t>
+  </si>
+  <si>
+    <t>'Worth watching as more data surfaces' is a weak close — it says nothing actionable to a first-time visitor.</t>
+  </si>
+  <si>
+    <t>Verified Peptides has eight Finnrick-verified tests and an active COA page, but the operator is nearly anonymous — no contact info, no address, no ownership disclosure. Purity data has not yet been captured from their COA archive, so the score reflects testing footprint rather than confirmed numbers. Not enough data to recommend. Score and status will be updated as additional documentation is reviewed.</t>
+  </si>
+  <si>
+    <t>Accurate but formulaic — nearly identical in structure to Simple Peptide, Verified Peptides, and Paramount verdicts. Risks reducing trust through apparent copy-paste.</t>
+  </si>
+  <si>
+    <t>Multiple verdicts in the 58–67 range follow the same exact structure: 'Finnrick tests + COA page + transparency gaps + no purity data.' Differentiate by what is specifically documented about this vendor.</t>
+  </si>
+  <si>
+    <t>Peptide Crafters has seven Finnrick-verified tests and an active COA page. Contact info is public. No physical address or ownership disclosure. Purity data is not in our database — the score reflects testing footprint and transparency signals rather than confirmed purity percentages. Documentation infrastructure is present but not fully mapped.</t>
+  </si>
+  <si>
+    <t>Technically the most detailed verdict in the dataset. Kovera Labs panel description is valuable for sophisticated researchers. The close sounds like an internal note.</t>
+  </si>
+  <si>
+    <t>Five testing method types listed consecutively reads as a spec sheet. 'Score will rise further if Kovera Labs accreditation is confirmed' introduces a conditional that should read as a factual current gap, not an upgrade invitation.</t>
+  </si>
+  <si>
+    <t>Ascension Peptides tests through Kovera Labs — a named third-party lab producing full-panel COAs with HPLC purity analysis, LC-MS identity confirmation, endotoxin screening, microbial sterility, and heavy metal testing. Purity across 50+ reviewed documents averages above 99.5%. COA access requires passing an age gate, which limits casual browsing but does not affect documentation quality. No physical address or ownership disclosure on file. Kovera Labs' ISO 17025 accreditation status is pending independent confirmation; score will be updated accordingly.</t>
+  </si>
+  <si>
+    <t>Specific and well-documented. The dual-testing note is a genuine differentiator correctly highlighted.</t>
+  </si>
+  <si>
+    <t>'Strong T3, approaching T4' reads as an internal grading note, not visitor copy. Confuses visitors unfamiliar with the tier system.</t>
+  </si>
+  <si>
+    <t>Felix Chemical Supply tests through two independently verified labs — Freedom Diagnostics and Chromate Analytical — with each batch entry labeled by which lab ran the analysis. A subset of batches are dual-tested by both labs on the same lot. Per-product COA pages contain full historical archives with batch-specific identifiers. Florida-based (Saint Augustine, FL). Pricing is at the low end of the market. The only transparency gap is ownership disclosure. Strong lab documentation for the price point.</t>
+  </si>
+  <si>
+    <t>Accurate. 'No COA archive' flag is clearly stated. The close is weak.</t>
+  </si>
+  <si>
+    <t>'Sufficient identity transparency for the score' sounds like score justification rather than a verdict.</t>
+  </si>
+  <si>
+    <t>Peptide Partners discloses ownership, publishes contact info, and has Finnrick-verified testing on file. No publicly accessible COA archive at time of review — documentation should be independently browsable, not just referenced. No physical address on file. Transparency at the company level is adequate; documentation at the product level needs work.</t>
+  </si>
+  <si>
+    <t>'The operator is completely anonymous' is appropriately direct. 'Worth watching, not ready to recommend' is a usable close.</t>
+  </si>
+  <si>
+    <t>Minor: 'completely anonymous' is a strong phrase given that a COA page does exist — someone is maintaining it. Verify accuracy.</t>
+  </si>
+  <si>
+    <t>Nuscience Peptides has ten Finnrick-verified tests — above average coverage for this tier. Free shipping on all orders. No contact info, no address, no ownership disclosure on file. A COA page exists but purity data has not been extracted. The testing footprint is real; the company behind it is unidentifiable by current documentation. Worth monitoring as more data surfaces, not currently recommended.</t>
+  </si>
+  <si>
+    <t>The BPC-157 failure data is the most alarming quality finding in the dataset — but the verdict buries it behind a positive framing of testing volume.</t>
+  </si>
+  <si>
+    <t>CRITICAL: The most important finding — catastrophic BPC-157 quality across 12 tests — is listed after a positive opening about testing footprint. A visitor scanning for BPC-157 vendors could miss the warning. Lead with the failure.</t>
+  </si>
+  <si>
+    <t>Skye Peptides has one of the largest Finnrick testing footprints in our database — 75 verified tests across 10 compounds. GLP-1 peptides (Semaglutide, Tirzepatide, Retatrutide) rate well. However, BPC-157 — their most popular product — has rated E Bad across 12 tests, with a minimum score of 2.6/10. That is not a borderline result. Ipamorelin and CJC-1295 score in the middle range. No contact info, no address, no ownership disclosure, and no lab named on-site. Do not buy BPC-157 from Skye Peptides.</t>
+  </si>
+  <si>
+    <t>Clear. 'One of the more complete identity profiles at this score level' is appropriate.</t>
+  </si>
+  <si>
+    <t>'Good baseline legitimacy' is weak phrasing — 'baseline' adds nothing and sounds generic.</t>
+  </si>
+  <si>
+    <t>Biotech Peptides has confirmed contact info, a physical address, and lab disclosure — a more complete identity profile than most vendors at this score level. COA page is active. No Finnrick testing and no purity data in our database. Operational transparency is solid; product quality cannot be independently verified from current data.</t>
+  </si>
+  <si>
+    <t>Brief and accurate. Appropriate given limited data.</t>
+  </si>
+  <si>
+    <t>Nearly identical structure to Biotech Peptides immediately above. Formulaic verdicts in the same score range reduce trust — visitors may suspect copy-paste.</t>
+  </si>
+  <si>
+    <t>Crush Research discloses ownership, publishes contact info, and maintains an active COA page. No Finnrick testing and no purity data in our database. Batch numbers are present but no third-party lab name has been confirmed. Company identity is documented; product quality has not been independently verified.</t>
+  </si>
+  <si>
+    <t>'A product at 57% purity is mostly not what it's labeled' is the second-best line in the dataset. Keep it exactly.</t>
+  </si>
+  <si>
+    <t>The semicolon construction — 'Do not buy CJC-1295 from Swiss Chems; the rest of the catalog requires more data' — makes a strong warning feel like a footnote. Split it.</t>
+  </si>
+  <si>
+    <t>Two CJC-1295 batches tested below 58% purity — not borderline results. A product at 57% purity is mostly not what it's labeled. Other tested peptides look cleaner, but the full catalog requires more data before recommending. Do not buy CJC-1295 from Swiss Chems. Contact info is public; no physical address or ownership on file.</t>
+  </si>
+  <si>
+    <t>The 'identity checks out; testing record needs work to justify the price premium' structure is effective and appropriately critical.</t>
+  </si>
+  <si>
+    <t>Minor: 'The identity checks out' is informal. The price premium point is the most useful visitor signal and could be stated more specifically.</t>
+  </si>
+  <si>
+    <t>Sports Technology Labs discloses both physical address and ownership — more accountability than most vendors at this score level. COA page is active. No Finnrick testing and no purity data in our database. Pricing runs at the high end of the market. For a vendor charging a premium, the testing record needs to catch up before the price is justified.</t>
+  </si>
+  <si>
+    <t>The SwiftCS explanation is useful and appropriate for a first-time visitor. Correct to include it.</t>
+  </si>
+  <si>
+    <t>'An unusual approach but a real one' hedges in a way that undercuts the point. Either explain the value or drop the qualifier.</t>
+  </si>
+  <si>
+    <t>Nexaph hosts COAs through SwiftCS (nexaph.coa.swiftcs.ai), a third-party COA verification platform. Ten Finnrick-verified tests add an independent confirmation layer. No address, no ownership disclosure, and no lab named on the vendor's own site. Above-market pricing. The Finnrick coverage is the strongest credibility signal here; company identity documentation is absent.</t>
+  </si>
+  <si>
+    <t>Cloudflare access issue disclosed honestly — appropriate for methodology transparency.</t>
+  </si>
+  <si>
+    <t>'One of the larger catalogs in this space' — size is stated without context that makes it meaningful to a visitor.</t>
+  </si>
+  <si>
+    <t>Pure Rawz has seven Finnrick-verified tests indicating a real lab testing relationship exists. The COA page was inaccessible at review time due to Cloudflare blocking, so current documentation cannot be confirmed. No contact info, no address, no ownership disclosure. For a vendor operating at this scale, the anonymity is a significant concern. Score will be updated when the COA page becomes accessible.</t>
+  </si>
+  <si>
+    <t>One of the better-written lower-tier verdicts. 'Right foundations...documentation accessibility needs work' is well-calibrated.</t>
+  </si>
+  <si>
+    <t>Minor: 'Score of 46 reflects a confirmed T3 lab with incomplete operational transparency' reads as score justification. Integrate more naturally.</t>
+  </si>
+  <si>
+    <t>True Research Labs tests through Horizon Analytical — a US-based lab producing UPLC/MS reports with batch-specific identifiers. Testing methodology is disclosed and results are accessible through per-product document links. Business address confirmed (Sheridan, WY). The COA page requires JavaScript navigation and results are not directly browsable without clicking through individual product pages. No ownership disclosure on file. The lab infrastructure is legitimate; documentation accessibility needs improvement before this vendor warrants a stronger score.</t>
+  </si>
+  <si>
+    <t>Vanguard ISO/IEC 17025 note is specific and credibility-building. Conditional score projection is analytically useful.</t>
+  </si>
+  <si>
+    <t>Cloudflare explanation inserts platform access limitations into the vendor verdict — appropriate transparency but may confuse visitors unfamiliar with why a review site couldn't access a public page.</t>
+  </si>
+  <si>
+    <t>Certified Pep uses Vanguard Laboratory — ISO/IEC 17025:2017 accredited — for purity, endotoxin, heavy metal, and bacterial testing. That is among the most specific lab disclosures in this tier. The site was Cloudflare-protected at review time, preventing direct verification of product catalog and pricing. Score reflects confirmed documentation rather than a full catalog review. If pricing and breadth are competitive, this vendor would likely score in the 45–60 range with full data access.</t>
+  </si>
+  <si>
+    <t>'T3 lab operating with a T1 disclosure profile' is sharp and useful. Keep it.</t>
+  </si>
+  <si>
+    <t>Minor: The Chromate Analytical confirmation is the most specific known fact about this vendor — it should lead, not follow the generic gap list.</t>
+  </si>
+  <si>
+    <t>Perfect Peptides uses Chromate Analytical for third-party testing — a confirmed lab with a public verification portal. Lab name and batch-specific documentation are present in reviewed COAs. The gap is surrounding transparency: no ownership disclosure, no business address, and limited community testing history. The lab is legitimate; the operational profile around it is thin. Not a vendor we can recommend on current data.</t>
+  </si>
+  <si>
+    <t>'Licensed Peptides Reports' issue — inability to confirm independent testing — is correctly identified as the most damaging finding. 10-vial pack pricing note is a useful consumer flag.</t>
+  </si>
+  <si>
+    <t>'Score will rise significantly if they publish the lab name' sounds like an invitation for the vendor to game the rating. Rephrase as a current gap, not an upgrade path.</t>
+  </si>
+  <si>
+    <t>Licensed Peptides has a confirmed physical address (Boca Raton, FL), a published phone number, and describes a multi-step verification process including HPLC, mass spec, endotoxin, and sterility checks. Lot numbers appear on purity reports. The critical gap: no third-party lab is named anywhere on the site. Purity reports are branded as 'Licensed Peptides Reports,' which means independent testing cannot be confirmed. The product catalog is sold exclusively in 10-vial packs, which inflates apparent pricing relative to per-vial vendors. Operational transparency is above average; lab independence is unverified.</t>
+  </si>
+  <si>
+    <t>'Not batch-specific' distinction is exactly the right nuance. Well-handled.</t>
+  </si>
+  <si>
+    <t>'A legitimate vendor with documentation that needs to go one level deeper' is slightly informal as a close.</t>
+  </si>
+  <si>
+    <t>Core Peptides uses third-party lab testing, with contact info and a physical address on file. COA page is active. No Finnrick testing. The current limitation is batch specificity — the same COA applies across multiple production runs, meaning individual lots cannot be independently traced. A real testing relationship exists; documentation needs to be batch-specific before the testing claim is fully supportable.</t>
+  </si>
+  <si>
+    <t>Best verdict in the dataset. Every claim is specific, the fraud indicators are clearly named, and the close is unambiguous. No changes needed.</t>
+  </si>
+  <si>
+    <t>None.</t>
+  </si>
+  <si>
+    <t>— No revision needed. This verdict should serve as the template for all fraud/anomaly findings across the database. —</t>
+  </si>
+  <si>
+    <t>Clear and appropriately brief given zero testing data.</t>
+  </si>
+  <si>
+    <t>Minor: 'Not recommended until testing documentation appears' is the right verdict but could name what specifically is needed.</t>
+  </si>
+  <si>
+    <t>LVLUP Health has no COA page and no lab testing documentation of any kind. Ownership is disclosed — the only verifiable transparency signal. Product quality cannot be evaluated from available data. Not recommended until third-party testing documentation is published.</t>
+  </si>
+  <si>
+    <t>The PayPal-only note is a useful consumer protection flag not present in other bottom-tier verdicts.</t>
+  </si>
+  <si>
+    <t>Minor: 'Which limits transaction protection compared to credit card purchases' is accurate but implies purchasing intent on a research-only platform. Keep it but note the tension.</t>
+  </si>
+  <si>
+    <t>Limitless Biotech has no COA page and no lab testing documentation. Contact info is public. Payments are accepted via PayPal only, which offers more limited dispute resolution than credit card transactions. Not enough evidence to evaluate product quality. Not recommended without third-party testing documentation.</t>
+  </si>
+  <si>
+    <t>Brief and appropriate.</t>
+  </si>
+  <si>
+    <t>Minor: 'Claims to offer research-grade peptides but provides no independent verification' could be more direct — the claim vs. evidence gap is the key finding.</t>
+  </si>
+  <si>
+    <t>Healthgevity has no COA page, no lab testing documentation, and no physical address on file. No independent verification of any kind is available. Not recommended.</t>
+  </si>
+  <si>
+    <t>Accurate. 'Internal testing only' flag is appropriately direct.</t>
+  </si>
+  <si>
+    <t>Minor: 'COA documents cannot be treated as reliable quality evidence' is accurate but slightly legalistic.</t>
+  </si>
+  <si>
+    <t>Penguin Peptides has an active COA page and a physical address on file. Testing is internal — no independent third-party lab has been identified. Without external verification, COA documents reflect vendor-reported results only. Not recommended for quality-sensitive purchases until independent testing is confirmed.</t>
+  </si>
+  <si>
+    <t>Appropriate. 'Listed for completeness' framing is honest.</t>
+  </si>
+  <si>
+    <t>Minor: 'Institutional-access-only catalog' may confuse visitors — briefly clarify what this means.</t>
+  </si>
+  <si>
+    <t>Alpha BioMed Labs operates an institutional-access-only catalog — products are not publicly available for purchase at this time. Listed for database completeness. No public documentation available for evaluation.</t>
+  </si>
+  <si>
+    <t>'Avoid' is the right verdict. Direct.</t>
+  </si>
+  <si>
+    <t>The list of negatives reads as a checklist. Condense without losing the severity.</t>
+  </si>
+  <si>
+    <t>Dynamic Peptide has no COA page, no lab testing, no contact information, no physical address, and no ownership disclosure. No basis exists for evaluating product quality. Avoid.</t>
+  </si>
+  <si>
+    <t>Clear. 'Lowest-scored vendor in our database' is a superlative that will become inaccurate as the database grows.</t>
+  </si>
+  <si>
+    <t>Drop the superlative — the Avoid verdict stands on its own.</t>
+  </si>
+  <si>
+    <t>Southern Peptides has no COA page, no lab testing, no contact information, no physical address, and no ownership disclosure. No documentation of any kind is available. Avoid.</t>
+  </si>
+  <si>
+    <t>'Score of 5 reflects no data, not confirmed problems' is an important and rare transparency note — prevents visitors from treating absence of evidence as evidence of fraud.</t>
+  </si>
+  <si>
+    <t>Minor: 'We recommend waiting for more information' is slightly informal.</t>
+  </si>
+  <si>
+    <t>Maxx Research Supply (maxxresearchsupply.com) was inaccessible at review time due to Cloudflare protection, is not indexed in public search, and has no presence in third-party review databases. No products, pricing, or documentation of any kind are verifiable. A score of 5 reflects an absence of available data, not confirmed fraud or product failures. Not recommended until documentation becomes accessible.</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -43,13 +790,31 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F4E79"/>
+        <bgColor rgb="FF1F4E79"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -64,14 +829,28 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -396,69 +1175,74 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K49"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:N49"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="28.83203125" customWidth="1"/>
     <col min="2" max="2" width="7.83203125" customWidth="1"/>
-    <col min="3" max="3" width="9.83203125" customWidth="1"/>
-    <col min="4" max="4" width="9.83203125" customWidth="1"/>
-    <col min="5" max="5" width="5.83203125" customWidth="1"/>
-    <col min="6" max="6" width="5.83203125" customWidth="1"/>
-    <col min="7" max="7" width="5.83203125" customWidth="1"/>
-    <col min="8" max="8" width="5.83203125" customWidth="1"/>
+    <col min="3" max="4" width="9.83203125" customWidth="1"/>
+    <col min="5" max="8" width="5.83203125" customWidth="1"/>
     <col min="9" max="9" width="80.83203125" customWidth="1"/>
-    <col min="10" max="10" width="60.83203125" customWidth="1"/>
-    <col min="11" max="11" width="12.83203125" customWidth="1"/>
+    <col min="10" max="11" width="45" customWidth="1"/>
+    <col min="12" max="12" width="60" customWidth="1"/>
+    <col min="13" max="13" width="60.83203125" customWidth="1"/>
+    <col min="14" max="14" width="12.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Vendor</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Score</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Status</v>
-      </c>
-      <c r="D1" t="str">
-        <v>COA Tier</v>
-      </c>
-      <c r="E1" t="str">
-        <v>LV</v>
-      </c>
-      <c r="F1" t="str">
-        <v>PQ</v>
-      </c>
-      <c r="G1" t="str">
-        <v>TR</v>
-      </c>
-      <c r="H1" t="str">
-        <v>CX</v>
-      </c>
-      <c r="I1" t="str">
-        <v>Verdict</v>
-      </c>
-      <c r="J1" t="str">
-        <v>Audit Notes</v>
-      </c>
-      <c r="K1" t="str">
-        <v>Audited At</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Bulk Peptide Supply</v>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="M1" t="s">
+        <v>9</v>
+      </c>
+      <c r="N1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" ht="65" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>11</v>
       </c>
       <c r="B2">
         <v>95</v>
       </c>
-      <c r="C2" t="str">
-        <v>active</v>
-      </c>
-      <c r="D2" t="str">
-        <v/>
+      <c r="C2" t="s">
+        <v>12</v>
       </c>
       <c r="E2">
         <v>35</v>
@@ -472,28 +1256,31 @@
       <c r="H2">
         <v>10</v>
       </c>
-      <c r="I2" t="str">
-        <v>Bulk Peptide Supply publicly discloses ownership, lists a physical address, and covers seven products through Finnrick-verified third-party testing — a cleaner transparency profile than most vendors at this score level. Average purity is 99.4% across seven tests. The gaps are minor: no published contact information, and test coverage is still relatively thin for a catalog of this size. A reliable baseline with room to grow.</v>
-      </c>
-      <c r="J2" t="str">
-        <v>T4 — Finnrick chain-of-custody, no audit required</v>
-      </c>
-      <c r="K2" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>Polaris Peptides</v>
+      <c r="I2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="M2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="91" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>15</v>
       </c>
       <c r="B3">
         <v>95</v>
       </c>
-      <c r="C3" t="str">
-        <v>active</v>
-      </c>
-      <c r="D3" t="str">
-        <v/>
+      <c r="C3" t="s">
+        <v>12</v>
       </c>
       <c r="E3">
         <v>38</v>
@@ -507,28 +1294,31 @@
       <c r="H3">
         <v>7</v>
       </c>
-      <c r="I3" t="str">
-        <v>Polaris runs COAs per product rather than linking to a single page — each listing has its own Chromate Analytics or Janoshik report, and nine products have Finnrick endotoxin test results on top of that. Purity data we've reviewed averages 99.4% across eleven tested peptides with no failures. Access to the COA page itself requires a free account login, which is an extra step but not unusual for a members-model vendor. Ownership is publicly disclosed. This is one of the most comprehensively documented vendors in our database.</v>
-      </c>
-      <c r="J3" t="str">
-        <v>T4 — Finnrick chain-of-custody, no audit required</v>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>EZ Peptides</v>
+      <c r="I3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="M3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="78" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>17</v>
       </c>
       <c r="B4">
         <v>93</v>
       </c>
-      <c r="C4" t="str">
-        <v>active</v>
-      </c>
-      <c r="D4" t="str">
-        <v/>
+      <c r="C4" t="s">
+        <v>12</v>
       </c>
       <c r="E4">
         <v>33</v>
@@ -542,28 +1332,31 @@
       <c r="H4">
         <v>10</v>
       </c>
-      <c r="I4" t="str">
-        <v>EZ Peptides publishes third-party lab results backed by Finnrick verification across six tested products, and the company lists a physical US address. Most purity results are solid, but one retatrutide batch came back at 93.2% — below the 95% threshold where we start flagging product quality. Whether that's a one-time outlier or a sign of inconsistency requires more data points. No named ownership. The testing infrastructure is real; we'd want to see that retatrutide result addressed before ranking this higher.</v>
-      </c>
-      <c r="J4" t="str">
-        <v>T4 — Finnrick chain-of-custody, no audit required</v>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>Orbitrex Peptides</v>
+      <c r="I4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="M4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="78" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>19</v>
       </c>
       <c r="B5">
         <v>86</v>
       </c>
-      <c r="C5" t="str">
-        <v>active</v>
-      </c>
-      <c r="D5" t="str">
-        <v/>
+      <c r="C5" t="s">
+        <v>12</v>
       </c>
       <c r="E5">
         <v>35</v>
@@ -577,28 +1370,31 @@
       <c r="H5">
         <v>10</v>
       </c>
-      <c r="I5" t="str">
-        <v>Orbitrex operates from Iceland, which means purchases fall outside US consumer protection frameworks — worth knowing before you order. On the chemistry side, the record is nearly spotless: 99.89% average purity across seven Finnrick-verified tests, with batch-specific COAs and methodology documentation. A physical address is on file but there's no published contact information. The jurisdiction risk is real; the testing evidence isn't.</v>
-      </c>
-      <c r="J5" t="str">
-        <v>T4 — Finnrick chain-of-custody, no audit required</v>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>NextechLabs</v>
+      <c r="I5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="M5" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" ht="78" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>21</v>
       </c>
       <c r="B6">
         <v>86</v>
       </c>
-      <c r="C6" t="str">
-        <v>active</v>
-      </c>
-      <c r="D6" t="str">
-        <v/>
+      <c r="C6" t="s">
+        <v>12</v>
       </c>
       <c r="E6">
         <v>35</v>
@@ -612,28 +1408,31 @@
       <c r="H6">
         <v>10</v>
       </c>
-      <c r="I6" t="str">
-        <v>NextechLabs has strong testing numbers — 99.69% average across seven Finnrick-verified products — but no publicly accessible COA archive. We couldn't locate an active COA page, which means the documentation exists in Finnrick's system but isn't independently browsable. No contact information, no ownership disclosure. The purity record is clean; the transparency infrastructure around it is thin. We'd want a working COA page before ranking this higher.</v>
-      </c>
-      <c r="J6" t="str">
-        <v>T4 — Finnrick chain-of-custody, no audit required</v>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>Aavant Research</v>
+      <c r="I6" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="M6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="78" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>23</v>
       </c>
       <c r="B7">
         <v>81</v>
       </c>
-      <c r="C7" t="str">
-        <v>active</v>
-      </c>
-      <c r="D7" t="str">
-        <v/>
+      <c r="C7" t="s">
+        <v>12</v>
       </c>
       <c r="E7">
         <v>35</v>
@@ -647,28 +1446,31 @@
       <c r="H7">
         <v>5</v>
       </c>
-      <c r="I7" t="str">
-        <v>Aavant Research posts some of the cleanest purity numbers in our dataset — 99.87% average across seven Finnrick-verified tests, including multiple tirzepatide and retatrutide runs. Contact information is public; no physical address or ownership disclosure. The testing record alone would rank them higher if the company identity were clearer. As it stands, you're buying from a well-tested vendor whose principals are unknown.</v>
-      </c>
-      <c r="J7" t="str">
-        <v>T4 — Finnrick chain-of-custody, no audit required</v>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>Omegamino</v>
+      <c r="I7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="M7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="91" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>25</v>
       </c>
       <c r="B8">
         <v>76</v>
       </c>
-      <c r="C8" t="str">
-        <v>active</v>
-      </c>
-      <c r="D8" t="str">
-        <v/>
+      <c r="C8" t="s">
+        <v>12</v>
       </c>
       <c r="E8">
         <v>30</v>
@@ -682,28 +1484,31 @@
       <c r="H8">
         <v>5</v>
       </c>
-      <c r="I8" t="str">
-        <v>Omegamino meets the basic requirements: third-party testing, batch numbers, methodology disclosed. Purity averages 99.8% across the four products we have data for, which is solid. But four Finnrick-verified tests is the minimum we'd accept, and there's no contact information, no physical address, and no ownership disclosure. The testing data is good; the company identity is a blank. Sufficient for cautious buyers, not a vendor we'd recommend over better-documented alternatives.</v>
-      </c>
-      <c r="J8" t="str">
-        <v>T4 — Finnrick chain-of-custody, no audit required</v>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>Astro Peptides</v>
+      <c r="I8" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="M8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" ht="78" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>27</v>
       </c>
       <c r="B9">
         <v>74</v>
       </c>
-      <c r="C9" t="str">
-        <v>active</v>
-      </c>
-      <c r="D9" t="str">
-        <v/>
+      <c r="C9" t="s">
+        <v>12</v>
       </c>
       <c r="E9">
         <v>35</v>
@@ -717,28 +1522,34 @@
       <c r="H9">
         <v>5</v>
       </c>
-      <c r="I9" t="str">
-        <v>Two CJC-1295 batches came back at 88.99% and 85.65% purity — the lowest results in our dataset for any vendor in this group. Both failures were from the same testing date, which suggests a bad batch rather than a systematic problem, but neither has been publicly acknowledged. Other tested products look clean. No COA page is publicly accessible, no contact information, and no address or ownership on file. The CJC-1295 results need an explanation before this vendor earns a stronger recommendation.</v>
-      </c>
-      <c r="J9" t="str">
-        <v>T4 — Finnrick chain-of-custody, no audit required</v>
-      </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>RUO Science</v>
+      <c r="I9" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="M9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="78" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>29</v>
       </c>
       <c r="B10">
         <v>68</v>
       </c>
-      <c r="C10" t="str">
-        <v>active</v>
-      </c>
-      <c r="D10" t="str">
-        <v>T3</v>
+      <c r="C10" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" t="s">
+        <v>30</v>
       </c>
       <c r="E10">
         <v>25</v>
@@ -752,28 +1563,34 @@
       <c r="H10">
         <v>7</v>
       </c>
-      <c r="I10" t="str">
-        <v>RUO Science uses Freedom Diagnostics as their third-party testing laboratory — a US-based lab with a public searchable COA archive. Batch-specific documents are accessible and show real purity data: BPC-157 at 99.12% and Tirzepatide at 99.74% in reviewed samples. Testing methodology includes HPLC, mass spectrometry, endotoxin, sterility, and heavy metals. No business address or ownership disclosure on the site, which limits accountability. The lab is now confirmed; the transparency gaps around the business itself remain. A solid testing record that was previously undersold by an earlier incomplete assessment.</v>
-      </c>
-      <c r="J10" t="str">
-        <v>Freedom Diagnostics confirmed via downloaded webp. Lot LCARN500-02122026-J, searchable at FreedomDiagnosticsTesting.com. HPLC-UV-MS, mass spec included, chromatogram present. Multiple labs used across product line (MB/VP batch prefixes suggest MZ Biolabs and Vanguard also).</v>
-      </c>
-      <c r="K10" t="str">
-        <v>2026-06-11</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>Simple Peptide</v>
+      <c r="I10" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="M10" t="s">
+        <v>32</v>
+      </c>
+      <c r="N10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="91" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>34</v>
       </c>
       <c r="B11">
         <v>67</v>
       </c>
-      <c r="C11" t="str">
-        <v>active</v>
-      </c>
-      <c r="D11" t="str">
-        <v/>
+      <c r="C11" t="s">
+        <v>12</v>
       </c>
       <c r="E11">
         <v>35</v>
@@ -787,28 +1604,34 @@
       <c r="H11">
         <v>7</v>
       </c>
-      <c r="I11" t="str">
-        <v>Simple Peptide has seven Finnrick-verified tests, an active COA page, contact info, a physical address, and lab methodology disclosed — a cleaner checklist than most vendors near this score. The gap is purity data: we haven't extracted raw numbers from their COA archive yet, so the score reflects Finnrick's independent testing footprint rather than confirmed purity percentages. No ownership disclosure.</v>
-      </c>
-      <c r="J11" t="str">
-        <v>T4 — Finnrick chain-of-custody, no audit required</v>
-      </c>
-      <c r="K11" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>Glacier Aminos</v>
+      <c r="I11" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="M11" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="65" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>36</v>
       </c>
       <c r="B12">
         <v>66</v>
       </c>
-      <c r="C12" t="str">
-        <v>active</v>
-      </c>
-      <c r="D12" t="str">
-        <v>T1</v>
+      <c r="C12" t="s">
+        <v>12</v>
+      </c>
+      <c r="D12" t="s">
+        <v>37</v>
       </c>
       <c r="E12">
         <v>25</v>
@@ -822,28 +1645,37 @@
       <c r="H12">
         <v>5</v>
       </c>
-      <c r="I12" t="str">
-        <v>Third-party testing through Kovera Labs and Freedom Diagnostics — two named labs, which is more lab diversification than most vendors at this score level. Three tests averaging 99.7% purity. Contact info is public; no physical address or ownership. The sample is thin for a full catalog recommendation but the existing results are clean.</v>
-      </c>
-      <c r="J12" t="str">
-        <v>batch numbers present; no known lab name found in page text or PDFs — may be vendor-branded</v>
-      </c>
-      <c r="K12" t="str">
-        <v>2026-06-11</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>Mile High Compounds</v>
+      <c r="I12" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="M12" t="s">
+        <v>39</v>
+      </c>
+      <c r="N12" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="65" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>40</v>
       </c>
       <c r="B13">
         <v>66</v>
       </c>
-      <c r="C13" t="str">
-        <v>active</v>
-      </c>
-      <c r="D13" t="str">
-        <v>T1</v>
+      <c r="C13" t="s">
+        <v>12</v>
+      </c>
+      <c r="D13" t="s">
+        <v>37</v>
       </c>
       <c r="E13">
         <v>25</v>
@@ -857,28 +1689,37 @@
       <c r="H13">
         <v>5</v>
       </c>
-      <c r="I13" t="str">
-        <v>Chromate Analytics COAs, five tests averaging 99.4% purity. Ownership is disclosed and a physical address is on file. Iceland-based operation (.is domain) — no US consumer protection recourse. No contact information published. The testing data is solid; the jurisdiction and missing contact info are the flags.</v>
-      </c>
-      <c r="J13" t="str">
-        <v>no known lab name found in page text or PDFs — may be vendor-branded</v>
-      </c>
-      <c r="K13" t="str">
-        <v>2026-06-11</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>Ion Peptide</v>
+      <c r="I13" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="M13" t="s">
+        <v>42</v>
+      </c>
+      <c r="N13" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="52" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>43</v>
       </c>
       <c r="B14">
         <v>66</v>
       </c>
-      <c r="C14" t="str">
-        <v>active</v>
-      </c>
-      <c r="D14" t="str">
-        <v>T1</v>
+      <c r="C14" t="s">
+        <v>12</v>
+      </c>
+      <c r="D14" t="s">
+        <v>37</v>
       </c>
       <c r="E14">
         <v>25</v>
@@ -892,28 +1733,34 @@
       <c r="H14">
         <v>5</v>
       </c>
-      <c r="I14" t="str">
-        <v>Three different named third-party labs — ILS Laboratories, Kovera Labs, and Freedom Diagnostics — across six tests averaging 99.7% purity. A physical address is on file. No contact info or ownership disclosure. The lab diversification is a genuine differentiator; most vendors this size pick one lab and stick with it.</v>
-      </c>
-      <c r="J14" t="str">
-        <v>no known lab name found in page text or PDFs — may be vendor-branded</v>
-      </c>
-      <c r="K14" t="str">
-        <v>2026-06-11</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>Paramount Peptides</v>
+      <c r="I14" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="M14" t="s">
+        <v>42</v>
+      </c>
+      <c r="N14" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="78" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>45</v>
       </c>
       <c r="B15">
         <v>66</v>
       </c>
-      <c r="C15" t="str">
-        <v>active</v>
-      </c>
-      <c r="D15" t="str">
-        <v/>
+      <c r="C15" t="s">
+        <v>12</v>
       </c>
       <c r="E15">
         <v>36</v>
@@ -927,28 +1774,31 @@
       <c r="H15">
         <v>5</v>
       </c>
-      <c r="I15" t="str">
-        <v>Paramount has more Finnrick endotoxin tests than most vendors above it in the rankings — eight total — and both a physical address and contact information are listed. The problem is purity data: we have none in our database. Whether that's a gap in our scraping or a sign that HPLC results aren't publicly available, we can't independently confirm product purity. No ownership disclosure. The infrastructure is there; the chemistry documentation needs to catch up.</v>
-      </c>
-      <c r="J15" t="str">
-        <v>T4 — Finnrick chain-of-custody, no audit required</v>
-      </c>
-      <c r="K15" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>Loti Labs</v>
+      <c r="I15" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="M15" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="78" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>47</v>
       </c>
       <c r="B16">
         <v>65</v>
       </c>
-      <c r="C16" t="str">
-        <v>active</v>
-      </c>
-      <c r="D16" t="str">
-        <v/>
+      <c r="C16" t="s">
+        <v>12</v>
       </c>
       <c r="E16">
         <v>35</v>
@@ -962,28 +1812,31 @@
       <c r="H16">
         <v>5</v>
       </c>
-      <c r="I16" t="str">
-        <v>Loti Labs is one of the more transparent operators in this space — ownership disclosed, contact info public, address on file, Finnrick-verified. That makes the CJC-1295 results harder to explain: two separate batches came back below 62% purity. At those levels the product is mostly something else. Their other tested peptides look clean. Until Loti addresses those CJC-1295 results publicly, we can't recommend them for that peptide specifically.</v>
-      </c>
-      <c r="J16" t="str">
-        <v>T4 — Finnrick chain-of-custody, no audit required</v>
-      </c>
-      <c r="K16" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>Peptidology</v>
+      <c r="I16" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="M16" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="78" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>49</v>
       </c>
       <c r="B17">
         <v>65</v>
       </c>
-      <c r="C17" t="str">
-        <v>active</v>
-      </c>
-      <c r="D17" t="str">
-        <v/>
+      <c r="C17" t="s">
+        <v>12</v>
       </c>
       <c r="E17">
         <v>35</v>
@@ -997,28 +1850,31 @@
       <c r="H17">
         <v>5</v>
       </c>
-      <c r="I17" t="str">
-        <v>Peptidology operates out of Scottsdale, AZ and runs third-party testing through an ISO-17025 accredited lab. Their COA library has 426 documents on file, all batch-specific. Purity average across seven tested products is 99.5% with no failures. Seven Finnrick-verified tests add an independent layer of confirmation. Ownership isn't disclosed, which is the only transparency gap in an otherwise strong profile. One of the better-documented vendors in this space.</v>
-      </c>
-      <c r="J17" t="str">
-        <v>T4 — Finnrick chain-of-custody, no audit required</v>
-      </c>
-      <c r="K17" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>Paradigm Peptides</v>
+      <c r="I17" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="L17" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="M17" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" ht="90" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>51</v>
       </c>
       <c r="B18">
         <v>63</v>
       </c>
-      <c r="C18" t="str">
-        <v>flagged</v>
-      </c>
-      <c r="D18" t="str">
-        <v/>
+      <c r="C18" t="s">
+        <v>52</v>
       </c>
       <c r="E18">
         <v>33</v>
@@ -1032,28 +1888,20 @@
       <c r="H18">
         <v>5</v>
       </c>
-      <c r="I18" t="str">
-        <v/>
-      </c>
-      <c r="J18" t="str">
-        <v>T4 — Finnrick chain-of-custody, no audit required</v>
-      </c>
-      <c r="K18" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>Verified Peptides</v>
+      <c r="I18" s="2"/>
+      <c r="M18" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" ht="78" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>53</v>
       </c>
       <c r="B19">
         <v>62</v>
       </c>
-      <c r="C19" t="str">
-        <v>active</v>
-      </c>
-      <c r="D19" t="str">
-        <v/>
+      <c r="C19" t="s">
+        <v>12</v>
       </c>
       <c r="E19">
         <v>36</v>
@@ -1067,28 +1915,31 @@
       <c r="H19">
         <v>10</v>
       </c>
-      <c r="I19" t="str">
-        <v>Eight Finnrick-verified tests and an active COA page, but the operator is almost entirely anonymous — no contact info, no address, no ownership disclosure. The Finnrick coverage is meaningful for confirming a lab testing relationship exists, but without purity data in our database we can't confirm the actual numbers. Worth watching as more data surfaces.</v>
-      </c>
-      <c r="J19" t="str">
-        <v>T4 — Finnrick chain-of-custody, no audit required</v>
-      </c>
-      <c r="K19" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="str">
-        <v>Peptide Crafters</v>
+      <c r="I19" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="L19" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="M19" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" ht="65" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>55</v>
       </c>
       <c r="B20">
         <v>61</v>
       </c>
-      <c r="C20" t="str">
-        <v>active</v>
-      </c>
-      <c r="D20" t="str">
-        <v/>
+      <c r="C20" t="s">
+        <v>12</v>
       </c>
       <c r="E20">
         <v>35</v>
@@ -1102,28 +1953,34 @@
       <c r="H20">
         <v>10</v>
       </c>
-      <c r="I20" t="str">
-        <v>Seven Finnrick-verified tests and an active COA page. Contact info is public. No physical address or ownership disclosure. We don't have purity data in our database from their COA archive, so the score is driven by Finnrick footprint rather than confirmed percentages. The infrastructure is there; the documentation needs to be more publicly accessible.</v>
-      </c>
-      <c r="J20" t="str">
-        <v>T4 — Finnrick chain-of-custody, no audit required</v>
-      </c>
-      <c r="K20" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="str">
-        <v>Ascension Peptides</v>
+      <c r="I20" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="L20" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="M20" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" ht="104" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>57</v>
       </c>
       <c r="B21">
         <v>61</v>
       </c>
-      <c r="C21" t="str">
-        <v>active</v>
-      </c>
-      <c r="D21" t="str">
-        <v>T3</v>
+      <c r="C21" t="s">
+        <v>12</v>
+      </c>
+      <c r="D21" t="s">
+        <v>30</v>
       </c>
       <c r="E21">
         <v>25</v>
@@ -1137,28 +1994,37 @@
       <c r="H21">
         <v>0</v>
       </c>
-      <c r="I21" t="str">
-        <v>Testing is conducted by Kovera Labs — a named third-party laboratory producing full-panel COAs with RP-HPLC chromatograms, LC-MS identity confirmation, endotoxin screening (≤0.5 EU/mL), microbial sterility, and heavy metal testing (As, Cd, Pb, Hg). Batch numbers are specific and dated. Purity results average above 99.5% across 50+ reviewed documents. The COA page sits behind an age gate, which limits casual browsing, but the documentation quality inside is among the higher-tier vendors reviewed. No physical address or ownership disclosure — that is the remaining transparency gap. Score will rise further if Kovera Labs accreditation is confirmed in the A2LA or PJLA registry.</v>
-      </c>
-      <c r="J21" t="str">
-        <v>Kovera Labs (KVR-2026-XXXXXX report numbers). Full COA panel: RP-HPLC purity, Net Content, LC-MS identity, endotoxin (≤0.5 EU/mL, PASS), microbial sterility, heavy metals (As/Cd/Pb/Hg). Real chromatograms visible. Batch-specific lot numbers. Accreditation (A2LA/PJLA) not yet verified — upgrade to T3 if Kovera Labs confirmed ISO 17025.</v>
-      </c>
-      <c r="K21" t="str">
-        <v>2026-06-11</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="str">
-        <v>Felix Chemical Supply</v>
+      <c r="I21" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="K21" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="L21" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="M21" t="s">
+        <v>59</v>
+      </c>
+      <c r="N21" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" ht="91" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>60</v>
       </c>
       <c r="B22">
         <v>60</v>
       </c>
-      <c r="C22" t="str">
-        <v>active</v>
-      </c>
-      <c r="D22" t="str">
-        <v>T3</v>
+      <c r="C22" t="s">
+        <v>12</v>
+      </c>
+      <c r="D22" t="s">
+        <v>30</v>
       </c>
       <c r="E22">
         <v>25</v>
@@ -1172,28 +2038,34 @@
       <c r="H22">
         <v>10</v>
       </c>
-      <c r="I22" t="str">
-        <v>Felix uses two independently verified labs — Freedom Diagnostics and Chromate Analytical — and labels each batch entry explicitly by which lab ran the test. A subset of batches are dual-tested by both labs on the same lot, which is a notably high verification standard. Per-product COA pages contain a full historical archive with batch-specific identifiers. Florida-based (Saint Augustine, FL). Pricing runs at the low end of the market. The primary gap is ownership disclosure, which is not public. Strong lab transparency for the price point.</v>
-      </c>
-      <c r="J22" t="str">
-        <v>Freedom Diagnostics (Freedom Labs) + Chromate Analytical (Chromate Labs) — both confirmed T3 labs. Per-batch COA pages with explicit lab labeling on each entry. Batch 081925-BPC-6 dual-tested by both labs simultaneously. Extensive historical archive across all products. Strong T3, approaching T4.</v>
-      </c>
-      <c r="K22" t="str">
-        <v>2026-06-11</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="str">
-        <v>Peptide Partners</v>
+      <c r="I22" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="K22" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="L22" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="M22" t="s">
+        <v>62</v>
+      </c>
+      <c r="N22" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" ht="65" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>63</v>
       </c>
       <c r="B23">
         <v>60</v>
       </c>
-      <c r="C23" t="str">
-        <v>active</v>
-      </c>
-      <c r="D23" t="str">
-        <v/>
+      <c r="C23" t="s">
+        <v>12</v>
       </c>
       <c r="E23">
         <v>35</v>
@@ -1207,28 +2079,31 @@
       <c r="H23">
         <v>0</v>
       </c>
-      <c r="I23" t="str">
-        <v>Ownership is disclosed, contact info is public, and Finnrick-verified testing backs the lab transparency claim. No publicly accessible COA page at the time of review, which is a gap — COA documentation should be independently browsable. No physical address on file. Sufficient identity transparency for the score, but the missing COA archive limits how much we can confirm independently.</v>
-      </c>
-      <c r="J23" t="str">
-        <v>T4 — Finnrick chain-of-custody, no audit required</v>
-      </c>
-      <c r="K23" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="str">
-        <v>Nuscience Peptides</v>
+      <c r="I23" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="K23" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="L23" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="M23" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" ht="78" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>65</v>
       </c>
       <c r="B24">
         <v>58</v>
       </c>
-      <c r="C24" t="str">
-        <v>active</v>
-      </c>
-      <c r="D24" t="str">
-        <v/>
+      <c r="C24" t="s">
+        <v>12</v>
       </c>
       <c r="E24">
         <v>40</v>
@@ -1242,28 +2117,31 @@
       <c r="H24">
         <v>10</v>
       </c>
-      <c r="I24" t="str">
-        <v>Ten Finnrick-verified tests. No company identity disclosed — no contact info, no address, no ownership. COA page exists but we have no purity data extracted from it. Free shipping on all orders. The Finnrick coverage is real, but the operator is completely anonymous. Worth watching, not ready to recommend.</v>
-      </c>
-      <c r="J24" t="str">
-        <v>T4 — Finnrick chain-of-custody, no audit required</v>
-      </c>
-      <c r="K24" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="str">
-        <v>Prime Peptides</v>
+      <c r="I24" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="K24" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="L24" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="M24" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" ht="90" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>67</v>
       </c>
       <c r="B25">
         <v>58</v>
       </c>
-      <c r="C25" t="str">
-        <v>flagged</v>
-      </c>
-      <c r="D25" t="str">
-        <v/>
+      <c r="C25" t="s">
+        <v>52</v>
       </c>
       <c r="E25">
         <v>35</v>
@@ -1277,28 +2155,20 @@
       <c r="H25">
         <v>5</v>
       </c>
-      <c r="I25" t="str">
-        <v/>
-      </c>
-      <c r="J25" t="str">
-        <v>T4 — Finnrick chain-of-custody, no audit required</v>
-      </c>
-      <c r="K25" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="str">
-        <v>Skye Peptides</v>
+      <c r="I25" s="2"/>
+      <c r="M25" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" ht="91" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>68</v>
       </c>
       <c r="B26">
         <v>58</v>
       </c>
-      <c r="C26" t="str">
-        <v>active</v>
-      </c>
-      <c r="D26" t="str">
-        <v/>
+      <c r="C26" t="s">
+        <v>12</v>
       </c>
       <c r="E26">
         <v>40</v>
@@ -1312,28 +2182,34 @@
       <c r="H26">
         <v>10</v>
       </c>
-      <c r="I26" t="str">
-        <v>Seventy-five Finnrick-verified tests across 10 compounds — one of the highest testing footprints we track. Results are mixed: GLP-1 peptides (Semaglutide, Tirzepatide, Retatrutide) score A Great, but BPC-157 — their most popular product — rates E Bad with a minimum score of 2.6/10 across 12 tests. Ipamorelin and CJC-1295 rate B and C respectively. Zero company identity: no contact info, no address, no ownership disclosure, no lab named on-site. High testing footprint, notable quality concerns on core healing peptides, no company identity whatsoever.</v>
-      </c>
-      <c r="J26" t="str">
-        <v>T4 — Finnrick chain-of-custody, no audit required</v>
-      </c>
-      <c r="K26" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="str">
-        <v>Biotech Peptides</v>
+      <c r="I26" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="K26" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="L26" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="M26" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" ht="65" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>70</v>
       </c>
       <c r="B27">
         <v>55</v>
       </c>
-      <c r="C27" t="str">
-        <v>active</v>
-      </c>
-      <c r="D27" t="str">
-        <v>T1</v>
+      <c r="C27" t="s">
+        <v>12</v>
+      </c>
+      <c r="D27" t="s">
+        <v>37</v>
       </c>
       <c r="E27">
         <v>25</v>
@@ -1347,28 +2223,37 @@
       <c r="H27">
         <v>5</v>
       </c>
-      <c r="I27" t="str">
-        <v>Contact info, a physical address, and lab disclosure are all confirmed — one of the more complete identity profiles at this score level. COA page is active. No Finnrick testing, and we have no purity data in our database. Good baseline legitimacy, but without confirmed purity numbers the chemistry side is unverified.</v>
-      </c>
-      <c r="J27" t="str">
-        <v>no known lab name found in page text or PDFs — may be vendor-branded</v>
-      </c>
-      <c r="K27" t="str">
-        <v>2026-06-11</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="str">
-        <v>Crush Research</v>
+      <c r="I27" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="K27" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="L27" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="M27" t="s">
+        <v>42</v>
+      </c>
+      <c r="N27" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" ht="52" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>72</v>
       </c>
       <c r="B28">
         <v>55</v>
       </c>
-      <c r="C28" t="str">
-        <v>active</v>
-      </c>
-      <c r="D28" t="str">
-        <v>T1</v>
+      <c r="C28" t="s">
+        <v>12</v>
+      </c>
+      <c r="D28" t="s">
+        <v>37</v>
       </c>
       <c r="E28">
         <v>25</v>
@@ -1382,28 +2267,34 @@
       <c r="H28">
         <v>5</v>
       </c>
-      <c r="I28" t="str">
-        <v>Ownership and contact info are both public, and the COA page is active. No Finnrick testing and no purity data in our database. The company identity is solid for this tier; the chemistry documentation isn't comprehensive enough to verify product quality independently.</v>
-      </c>
-      <c r="J28" t="str">
-        <v>batch numbers present; no known lab name found in page text or PDFs — may be vendor-branded</v>
-      </c>
-      <c r="K28" t="str">
-        <v>2026-06-11</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="str">
-        <v>Swiss Chems</v>
+      <c r="I28" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="K28" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="L28" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="M28" t="s">
+        <v>39</v>
+      </c>
+      <c r="N28" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" ht="65" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>74</v>
       </c>
       <c r="B29">
         <v>51</v>
       </c>
-      <c r="C29" t="str">
-        <v>active</v>
-      </c>
-      <c r="D29" t="str">
-        <v/>
+      <c r="C29" t="s">
+        <v>12</v>
       </c>
       <c r="E29">
         <v>35</v>
@@ -1417,28 +2308,34 @@
       <c r="H29">
         <v>0</v>
       </c>
-      <c r="I29" t="str">
-        <v>Two CJC-1295 batches tested below 58% purity — not borderline results, these are failures. A product at 57% purity is mostly not what it's labeled. Other tested peptides look cleaner. Contact info is public, but no physical address or ownership. Do not buy CJC-1295 from Swiss Chems; the rest of the catalog requires more data before recommending.</v>
-      </c>
-      <c r="J29" t="str">
-        <v>T4 — Finnrick chain-of-custody, no audit required</v>
-      </c>
-      <c r="K29" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="str">
-        <v>Sports Technology Labs</v>
+      <c r="I29" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="K29" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="L29" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="M29" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" ht="65" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>76</v>
       </c>
       <c r="B30">
         <v>50</v>
       </c>
-      <c r="C30" t="str">
-        <v>active</v>
-      </c>
-      <c r="D30" t="str">
-        <v>T3</v>
+      <c r="C30" t="s">
+        <v>12</v>
+      </c>
+      <c r="D30" t="s">
+        <v>30</v>
       </c>
       <c r="E30">
         <v>25</v>
@@ -1452,28 +2349,34 @@
       <c r="H30">
         <v>0</v>
       </c>
-      <c r="I30" t="str">
-        <v>Physical address and ownership both disclosed — more accountability than most vendors near this score. COA page is active. No Finnrick testing, no purity data in our database. Pricing runs at the high end of the market. The identity checks out; the testing record needs work to justify the price premium.</v>
-      </c>
-      <c r="J30" t="str">
-        <v>MZ Biolabs COA confirmed via downloaded webp. Lot number 2025-10-06, HPLC-UV-MS, analyst Ken Pendarvis ChE. Real chromatogram with baseline noise. QR proof-of-authenticity.</v>
-      </c>
-      <c r="K30" t="str">
-        <v>2026-06-11</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="str">
-        <v>Nexaph</v>
+      <c r="I30" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="K30" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="L30" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="M30" t="s">
+        <v>78</v>
+      </c>
+      <c r="N30" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" ht="65" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>79</v>
       </c>
       <c r="B31">
         <v>48</v>
       </c>
-      <c r="C31" t="str">
-        <v>active</v>
-      </c>
-      <c r="D31" t="str">
-        <v/>
+      <c r="C31" t="s">
+        <v>12</v>
       </c>
       <c r="E31">
         <v>40</v>
@@ -1487,28 +2390,31 @@
       <c r="H31">
         <v>0</v>
       </c>
-      <c r="I31" t="str">
-        <v>COAs are hosted on SwiftCS (nexaph.coa.swiftcs.ai), a third-party COA verification platform — an unusual approach but a real one. Ten Finnrick-verified tests. No address, no ownership, and no lab named on the vendor's own site. Above-market pricing. The Finnrick coverage is the strongest signal here; everything else about the company identity is absent.</v>
-      </c>
-      <c r="J31" t="str">
-        <v>T4 — Finnrick chain-of-custody, no audit required</v>
-      </c>
-      <c r="K31" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="str">
-        <v>Pure Rawz</v>
+      <c r="I31" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="J31" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="K31" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="L31" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="M31" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" ht="78" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>81</v>
       </c>
       <c r="B32">
         <v>48</v>
       </c>
-      <c r="C32" t="str">
-        <v>active</v>
-      </c>
-      <c r="D32" t="str">
-        <v/>
+      <c r="C32" t="s">
+        <v>12</v>
       </c>
       <c r="E32">
         <v>35</v>
@@ -1522,28 +2428,34 @@
       <c r="H32">
         <v>5</v>
       </c>
-      <c r="I32" t="str">
-        <v>Seven Finnrick-verified tests suggest a real lab testing relationship exists. The COA page was inaccessible at review time — Cloudflare blocking — so we can't confirm what's there. No contact info, no address, no ownership. One of the larger catalogs in this space; the anonymity is a significant concern given the scale of the operation.</v>
-      </c>
-      <c r="J32" t="str">
-        <v>T4 — Finnrick chain-of-custody, no audit required</v>
-      </c>
-      <c r="K32" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="str">
-        <v>True Research Labs</v>
+      <c r="I32" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="J32" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="K32" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="L32" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="M32" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" ht="91" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>83</v>
       </c>
       <c r="B33">
         <v>46</v>
       </c>
-      <c r="C33" t="str">
-        <v>active</v>
-      </c>
-      <c r="D33" t="str">
-        <v>T3</v>
+      <c r="C33" t="s">
+        <v>12</v>
+      </c>
+      <c r="D33" t="s">
+        <v>30</v>
       </c>
       <c r="E33">
         <v>25</v>
@@ -1557,28 +2469,37 @@
       <c r="H33">
         <v>5</v>
       </c>
-      <c r="I33" t="str">
-        <v>COAs are tested by Horizon Analytical — a US-based lab issuing UPLC/MS reports with batch-specific identifiers. Testing methodology is disclosed and results are accessible through per-product document links. Business address confirmed (Sheridan, WY). However, the COA page requires JavaScript navigation and results are not browsable without clicking through individual product buttons. Ownership disclosure is absent. Score of 46 reflects a confirmed T3 lab with incomplete operational transparency. The right foundations are in place; documentation accessibility needs work before this vendor warrants a stronger recommendation.</v>
-      </c>
-      <c r="J33" t="str">
-        <v>Horizon Analytical confirmed via PDF download. Lot TRL-9907743, Aleksey Yevtodiyenko PhD. UPLC/MS, full chromatogram + mass spec on page 2. Searchable at horizonanalytical.com. Analysis date 05/12/2026.</v>
-      </c>
-      <c r="K33" t="str">
-        <v>2026-06-11</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="str">
-        <v>Certified Pep</v>
+      <c r="I33" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="J33" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="K33" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="L33" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="M33" t="s">
+        <v>85</v>
+      </c>
+      <c r="N33" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" ht="91" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>86</v>
       </c>
       <c r="B34">
         <v>43</v>
       </c>
-      <c r="C34" t="str">
-        <v>active</v>
-      </c>
-      <c r="D34" t="str">
-        <v>T3</v>
+      <c r="C34" t="s">
+        <v>12</v>
+      </c>
+      <c r="D34" t="s">
+        <v>30</v>
       </c>
       <c r="E34">
         <v>25</v>
@@ -1592,28 +2513,34 @@
       <c r="H34">
         <v>2</v>
       </c>
-      <c r="I34" t="str">
-        <v>Certified Pep uses Vanguard Laboratory — ISO/IEC 17025:2017 accredited, with named testing for purity, endotoxins, heavy metals, and bacteria. That's one of the most specific lab disclosures in this tier. Site is Cloudflare-protected so products and pricing couldn't be directly verified; score reflects the transparency record rather than a full catalog review. If pricing and product breadth are competitive, this vendor would score in the 45–60 range once we can access the full data. The lab disclosure alone puts them above most vendors at a similar overall score.</v>
-      </c>
-      <c r="J34" t="str">
-        <v>Lab: Vanguard; batch numbers present</v>
-      </c>
-      <c r="K34" t="str">
-        <v>2026-06-11</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="str">
-        <v>Amino Asylum</v>
+      <c r="I34" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="J34" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="K34" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="L34" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="M34" t="s">
+        <v>88</v>
+      </c>
+      <c r="N34" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" ht="90" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>89</v>
       </c>
       <c r="B35">
         <v>41</v>
       </c>
-      <c r="C35" t="str">
-        <v>flagged</v>
-      </c>
-      <c r="D35" t="str">
-        <v/>
+      <c r="C35" t="s">
+        <v>52</v>
       </c>
       <c r="E35">
         <v>36</v>
@@ -1627,28 +2554,23 @@
       <c r="H35">
         <v>5</v>
       </c>
-      <c r="I35" t="str">
-        <v/>
-      </c>
-      <c r="J35" t="str">
-        <v>T4 — Finnrick chain-of-custody, no audit required</v>
-      </c>
-      <c r="K35" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="str">
-        <v>Perfect Peptides</v>
+      <c r="I35" s="2"/>
+      <c r="M35" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" ht="78" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>90</v>
       </c>
       <c r="B36">
         <v>38</v>
       </c>
-      <c r="C36" t="str">
-        <v>active</v>
-      </c>
-      <c r="D36" t="str">
-        <v>T3</v>
+      <c r="C36" t="s">
+        <v>12</v>
+      </c>
+      <c r="D36" t="s">
+        <v>30</v>
       </c>
       <c r="E36">
         <v>25</v>
@@ -1662,28 +2584,37 @@
       <c r="H36">
         <v>5</v>
       </c>
-      <c r="I36" t="str">
-        <v>COAs are tested by Chromate Analytical, confirmed via direct document inspection. Lab name and batch information are present in reviewed documents. The score of 38 reflects near-zero purity data in our database and incomplete transparency flags — no ownership disclosure, no business address, and no community testing record. The lab is legitimate; the surrounding documentation infrastructure is not built out. A T3 lab operating with a T1 disclosure profile. Worth monitoring as data accumulates, not a vendor we can recommend yet.</v>
-      </c>
-      <c r="J36" t="str">
-        <v>Chromate Analytical confirmed via downloaded PNG. Certificate #34141, access PERFECT88HGR at chromate.org/verify. Batch PP6896266. Full panel: purity 99.294%, endotoxins 7.65 EU/vial, metals &lt;5ppb. Chromatogram present.</v>
-      </c>
-      <c r="K36" t="str">
-        <v>2026-06-11</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="str">
-        <v>Licensed Peptides</v>
+      <c r="I36" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="J36" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="K36" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="L36" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="M36" t="s">
+        <v>92</v>
+      </c>
+      <c r="N36" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" ht="104" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>93</v>
       </c>
       <c r="B37">
         <v>38</v>
       </c>
-      <c r="C37" t="str">
-        <v>active</v>
-      </c>
-      <c r="D37" t="str">
-        <v>T2</v>
+      <c r="C37" t="s">
+        <v>12</v>
+      </c>
+      <c r="D37" t="s">
+        <v>94</v>
       </c>
       <c r="E37">
         <v>15</v>
@@ -1697,28 +2628,34 @@
       <c r="H37">
         <v>7</v>
       </c>
-      <c r="I37" t="str">
-        <v>Licensed Peptides has a confirmed physical address (Boca Raton, FL), a phone number, and describes a 6-point verification process (HPLC, mass spec, endotoxin, sterility checks). Lot numbers appear on purity reports. The problem: no third-party testing lab is ever named — the purity reports are branded as 'Licensed Peptides Reports,' which means we can't confirm the testing was done by an independent party. The product catalog is also sold exclusively in 10-vial packs, which inflates apparent pricing relative to per-vial vendors. Good operational transparency, weak lab independence. Score will rise significantly if they publish the lab name.</v>
-      </c>
-      <c r="J37" t="str">
-        <v>Vanguard Laboratory COAs confirmed visually — legitimate lab, ISO 17025, A2LA #6377.01. BUT lot numbers are cap colors (Red Cap, Green Cap) not batch IDs — fails batch traceability. T2 until proper lot numbers confirmed. Chromatogram obscured by Licensed Peptides watermark.</v>
-      </c>
-      <c r="K37" t="str">
-        <v>2026-06-11</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="str">
-        <v>Core Peptides</v>
+      <c r="I37" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="J37" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="K37" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="L37" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="M37" t="s">
+        <v>96</v>
+      </c>
+      <c r="N37" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" ht="78" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>97</v>
       </c>
       <c r="B38">
         <v>33</v>
       </c>
-      <c r="C38" t="str">
-        <v>active</v>
-      </c>
-      <c r="D38" t="str">
-        <v/>
+      <c r="C38" t="s">
+        <v>12</v>
       </c>
       <c r="E38">
         <v>15</v>
@@ -1732,28 +2669,31 @@
       <c r="H38">
         <v>2</v>
       </c>
-      <c r="I38" t="str">
-        <v>Third-party lab testing with contact info and a physical address on file. COA page is active. No Finnrick testing. The lab verification is real but not batch-specific — meaning the same COA applies to multiple production runs, which limits how precisely you can trace what you're getting. A legitimate vendor with documentation that needs to go one level deeper.</v>
-      </c>
-      <c r="J38" t="str">
-        <v/>
-      </c>
-      <c r="K38" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="str">
-        <v>Cernum Biosciences</v>
+      <c r="I38" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="J38" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="K38" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="L38" s="2" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" ht="78" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>99</v>
       </c>
       <c r="B39">
         <v>28</v>
       </c>
-      <c r="C39" t="str">
-        <v>active</v>
-      </c>
-      <c r="D39" t="str">
-        <v>T1</v>
+      <c r="C39" t="s">
+        <v>12</v>
+      </c>
+      <c r="D39" t="s">
+        <v>37</v>
       </c>
       <c r="E39">
         <v>5</v>
@@ -1767,28 +2707,34 @@
       <c r="H39">
         <v>5</v>
       </c>
-      <c r="I39" t="str">
-        <v>Cernum Biosciences lists certificates of analysis on their website, but those COAs are issued by their own internal "Lab Research Department" — not an independent third-party lab. Every product on the site carries the identical batch number (201-139-35496), which means their batch tracking is a template, not a real audit trail. A 2026 press release placed on USA Today's paid wire service claims "independent third-party verification" and "batch-level traceability" — both directly contradicted by the actual COA documents. Cernum is a newer vendor with no community track record. Until genuine third-party lab results appear, we recommend looking elsewhere.</v>
-      </c>
-      <c r="J39" t="str">
-        <v>no known lab name found in page text or PDFs — may be vendor-branded</v>
-      </c>
-      <c r="K39" t="str">
-        <v>2026-06-11</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="str">
-        <v>LVLUP Health</v>
+      <c r="I39" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="J39" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="K39" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="L39" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="M39" t="s">
+        <v>42</v>
+      </c>
+      <c r="N39" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" ht="52" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>101</v>
       </c>
       <c r="B40">
         <v>21</v>
       </c>
-      <c r="C40" t="str">
-        <v>active</v>
-      </c>
-      <c r="D40" t="str">
-        <v/>
+      <c r="C40" t="s">
+        <v>12</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -1802,28 +2748,31 @@
       <c r="H40">
         <v>5</v>
       </c>
-      <c r="I40" t="str">
-        <v>No COA page and no lab testing documentation of any kind. Ownership is disclosed. There's not enough evidence to evaluate product quality — we can verify who runs it but not what they're selling. Not recommended until testing documentation appears.</v>
-      </c>
-      <c r="J40" t="str">
-        <v>T0 — no COA exists, nothing to verify</v>
-      </c>
-      <c r="K40" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="str">
-        <v>Limitless Biotech</v>
+      <c r="I40" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="J40" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="K40" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="L40" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="M40" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" ht="52" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
+        <v>104</v>
       </c>
       <c r="B41">
         <v>21</v>
       </c>
-      <c r="C41" t="str">
-        <v>active</v>
-      </c>
-      <c r="D41" t="str">
-        <v/>
+      <c r="C41" t="s">
+        <v>12</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -1837,28 +2786,31 @@
       <c r="H41">
         <v>5</v>
       </c>
-      <c r="I41" t="str">
-        <v>No COA page, no lab testing documentation. Contact info is public. Payments are PayPal-only, which limits transaction protection compared to credit card purchases. Not enough evidence to evaluate product quality. Not recommended without third-party testing.</v>
-      </c>
-      <c r="J41" t="str">
-        <v>T0 — no COA exists, nothing to verify</v>
-      </c>
-      <c r="K41" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="str">
-        <v>Healthgevity</v>
+      <c r="I41" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="J41" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="K41" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="L41" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="M41" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" ht="39" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>106</v>
       </c>
       <c r="B42">
         <v>13</v>
       </c>
-      <c r="C42" t="str">
-        <v>active</v>
-      </c>
-      <c r="D42" t="str">
-        <v/>
+      <c r="C42" t="s">
+        <v>12</v>
       </c>
       <c r="E42">
         <v>0</v>
@@ -1872,28 +2824,34 @@
       <c r="H42">
         <v>5</v>
       </c>
-      <c r="I42" t="str">
-        <v>No COA page, no lab testing, no physical address. Claims to offer research-grade peptides but provides no independent verification. Not recommended.</v>
-      </c>
-      <c r="J42" t="str">
-        <v>T0 — no COA exists, nothing to verify</v>
-      </c>
-      <c r="K42" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="str">
-        <v>Penguin Peptides</v>
+      <c r="I42" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="J42" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="K42" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="L42" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="M42" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" ht="65" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
+        <v>108</v>
       </c>
       <c r="B43">
         <v>13</v>
       </c>
-      <c r="C43" t="str">
-        <v>active</v>
-      </c>
-      <c r="D43" t="str">
-        <v>T1</v>
+      <c r="C43" t="s">
+        <v>12</v>
+      </c>
+      <c r="D43" t="s">
+        <v>37</v>
       </c>
       <c r="E43">
         <v>5</v>
@@ -1907,28 +2865,34 @@
       <c r="H43">
         <v>0</v>
       </c>
-      <c r="I43" t="str">
-        <v>COA page exists, and a physical address is on file. No third-party lab verification — internal testing only. No Finnrick testing. Without independent confirmation, the COA documents cannot be treated as reliable quality evidence.</v>
-      </c>
-      <c r="J43" t="str">
-        <v>no known lab name found in page text or PDFs — may be vendor-branded</v>
-      </c>
-      <c r="K43" t="str">
-        <v>2026-06-11</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="str">
-        <v>Alpha BioMed Labs</v>
+      <c r="I43" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="J43" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="K43" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="L43" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="M43" t="s">
+        <v>42</v>
+      </c>
+      <c r="N43" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" ht="39" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
+        <v>110</v>
       </c>
       <c r="B44">
         <v>13</v>
       </c>
-      <c r="C44" t="str">
-        <v>active</v>
-      </c>
-      <c r="D44" t="str">
-        <v/>
+      <c r="C44" t="s">
+        <v>12</v>
       </c>
       <c r="E44">
         <v>0</v>
@@ -1942,28 +2906,31 @@
       <c r="H44">
         <v>5</v>
       </c>
-      <c r="I44" t="str">
-        <v>Institutional-access-only catalog — products are not publicly purchasable at this time. Listed for completeness. No public documentation available to evaluate.</v>
-      </c>
-      <c r="J44" t="str">
-        <v>T0 — no COA exists, nothing to verify</v>
-      </c>
-      <c r="K44" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="str">
-        <v>Dynamic Peptide</v>
+      <c r="I44" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="J44" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="K44" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="L44" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="M44" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" ht="39" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
+        <v>112</v>
       </c>
       <c r="B45">
         <v>13</v>
       </c>
-      <c r="C45" t="str">
-        <v>active</v>
-      </c>
-      <c r="D45" t="str">
-        <v/>
+      <c r="C45" t="s">
+        <v>12</v>
       </c>
       <c r="E45">
         <v>0</v>
@@ -1977,28 +2944,31 @@
       <c r="H45">
         <v>5</v>
       </c>
-      <c r="I45" t="str">
-        <v>No COA, no lab testing of any kind, no contact info, no address, no ownership disclosure. One of the least-documented vendors in our database. We have no basis for evaluating product quality. Avoid.</v>
-      </c>
-      <c r="J45" t="str">
-        <v>T0 — no COA exists, nothing to verify</v>
-      </c>
-      <c r="K45" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="str">
-        <v>Southern Peptides</v>
+      <c r="I45" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="J45" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="K45" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="L45" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="M45" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" ht="39" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
+        <v>114</v>
       </c>
       <c r="B46">
         <v>10</v>
       </c>
-      <c r="C46" t="str">
-        <v>active</v>
-      </c>
-      <c r="D46" t="str">
-        <v/>
+      <c r="C46" t="s">
+        <v>12</v>
       </c>
       <c r="E46">
         <v>0</v>
@@ -2012,28 +2982,31 @@
       <c r="H46">
         <v>10</v>
       </c>
-      <c r="I46" t="str">
-        <v>No documentation of any kind: no COA, no lab testing, no contact info, no address, no ownership. Lowest-scored vendor in our database. Avoid.</v>
-      </c>
-      <c r="J46" t="str">
-        <v>T0 — no COA exists, nothing to verify</v>
-      </c>
-      <c r="K46" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="str">
-        <v>Maxx Research Supply</v>
+      <c r="I46" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="J46" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="K46" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="L46" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="M46" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14" ht="78" x14ac:dyDescent="0.2">
+      <c r="A47" t="s">
+        <v>116</v>
       </c>
       <c r="B47">
         <v>5</v>
       </c>
-      <c r="C47" t="str">
-        <v>active</v>
-      </c>
-      <c r="D47" t="str">
-        <v/>
+      <c r="C47" t="s">
+        <v>12</v>
       </c>
       <c r="E47">
         <v>0</v>
@@ -2047,28 +3020,31 @@
       <c r="H47">
         <v>5</v>
       </c>
-      <c r="I47" t="str">
-        <v>Maxx Research Supply (maxxresearchsupply.com) could not be accessed due to Cloudflare protection, is not indexed in public search, and has no presence in third-party review databases. No products, no prices, and no documentation of any kind are verifiable. Score of 5 reflects no data, not confirmed problems. We recommend waiting for more information before using this vendor.</v>
-      </c>
-      <c r="J47" t="str">
-        <v>T0 — no COA exists, nothing to verify</v>
-      </c>
-      <c r="K47" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="str">
-        <v>Apollo Peptide Sciences</v>
+      <c r="I47" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="J47" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="K47" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="L47" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="M47" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14" ht="90" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" t="s">
+        <v>118</v>
       </c>
       <c r="B48">
         <v>5</v>
       </c>
-      <c r="C48" t="str">
-        <v>active</v>
-      </c>
-      <c r="D48" t="str">
-        <v/>
+      <c r="C48" t="s">
+        <v>12</v>
       </c>
       <c r="E48">
         <v>0</v>
@@ -2082,28 +3058,19 @@
       <c r="H48">
         <v>5</v>
       </c>
-      <c r="I48" t="str">
-        <v/>
-      </c>
-      <c r="J48" t="str">
-        <v>T0 — no COA exists, nothing to verify</v>
-      </c>
-      <c r="K48" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="str">
-        <v>Pivot Labs</v>
+      <c r="M48" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" ht="90" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A49" t="s">
+        <v>119</v>
       </c>
       <c r="B49">
         <v>5</v>
       </c>
-      <c r="C49" t="str">
-        <v>active</v>
-      </c>
-      <c r="D49" t="str">
-        <v/>
+      <c r="C49" t="s">
+        <v>12</v>
       </c>
       <c r="E49">
         <v>0</v>
@@ -2117,19 +3084,11 @@
       <c r="H49">
         <v>5</v>
       </c>
-      <c r="I49" t="str">
-        <v/>
-      </c>
-      <c r="J49" t="str">
-        <v>T0 — no COA exists, nothing to verify</v>
-      </c>
-      <c r="K49" t="str">
-        <v/>
+      <c r="M49" t="s">
+        <v>103</v>
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K49"/>
-  </ignoredErrors>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>